--- a/input/2026H1线上投放与平台费用.xlsx
+++ b/input/2026H1线上投放与平台费用.xlsx
@@ -546,58 +546,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>116191.38</v>
+        <v>175791.83</v>
       </c>
       <c r="E2" t="n">
         <v>5913.57</v>
       </c>
       <c r="F2" t="n">
-        <v>110277.81</v>
+        <v>169878.26</v>
       </c>
       <c r="G2" t="n">
-        <v>85428.64</v>
+        <v>130259.98</v>
       </c>
       <c r="H2" t="n">
-        <v>24849.17</v>
+        <v>39618.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2253</v>
+        <v>0.2332</v>
       </c>
       <c r="J2" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="K2" t="n">
-        <v>934.5599999999999</v>
+        <v>1110.32</v>
       </c>
       <c r="L2" t="n">
-        <v>26406.57</v>
+        <v>39951.84</v>
       </c>
       <c r="M2" t="n">
-        <v>1550.67</v>
+        <v>2389.31</v>
       </c>
       <c r="N2" t="n">
-        <v>277.42</v>
+        <v>414.31</v>
       </c>
       <c r="O2" t="n">
-        <v>348.57</v>
+        <v>527.38</v>
       </c>
       <c r="P2" t="n">
-        <v>4066.7</v>
+        <v>6152.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>437.44</v>
+        <v>567.1900000000001</v>
       </c>
       <c r="R2" t="n">
         <v>1099.94</v>
       </c>
       <c r="S2" t="n">
-        <v>645.38</v>
+        <v>976.4299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>34832.69</v>
+        <v>52079.11</v>
       </c>
       <c r="U2" t="n">
-        <v>-9983.52</v>
+        <v>-12460.83</v>
       </c>
     </row>
     <row r="3">
@@ -617,58 +617,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112816.99</v>
+        <v>140450.58</v>
       </c>
       <c r="E3" t="n">
         <v>4192.05</v>
       </c>
       <c r="F3" t="n">
-        <v>108624.94</v>
+        <v>136258.53</v>
       </c>
       <c r="G3" t="n">
-        <v>80207.08</v>
+        <v>100391.29</v>
       </c>
       <c r="H3" t="n">
-        <v>28417.86</v>
+        <v>35867.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2616</v>
+        <v>0.2632</v>
       </c>
       <c r="J3" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="K3" t="n">
-        <v>944.5599999999999</v>
+        <v>973.28</v>
       </c>
       <c r="L3" t="n">
-        <v>26955.47</v>
+        <v>33557.99</v>
       </c>
       <c r="M3" t="n">
-        <v>1543.65</v>
+        <v>1945.28</v>
       </c>
       <c r="N3" t="n">
-        <v>262.81</v>
+        <v>325.86</v>
       </c>
       <c r="O3" t="n">
-        <v>338.45</v>
+        <v>421.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3948.59</v>
+        <v>4915.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>392.26</v>
+        <v>477.54</v>
       </c>
       <c r="R3" t="n">
         <v>464.21</v>
       </c>
       <c r="S3" t="n">
-        <v>539.46</v>
+        <v>671.6</v>
       </c>
       <c r="T3" t="n">
-        <v>34444.91</v>
+        <v>42779.6</v>
       </c>
       <c r="U3" t="n">
-        <v>-6027.05</v>
+        <v>-6912.36</v>
       </c>
     </row>
     <row r="4">
@@ -688,58 +688,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>138805.15</v>
+        <v>131216.4</v>
       </c>
       <c r="E4" t="n">
         <v>14672.75</v>
       </c>
       <c r="F4" t="n">
-        <v>124132.4</v>
+        <v>116543.65</v>
       </c>
       <c r="G4" t="n">
-        <v>101595.19</v>
+        <v>95149.35000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>22537.21</v>
+        <v>21394.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1816</v>
+        <v>0.1836</v>
       </c>
       <c r="J4" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K4" t="n">
-        <v>933.33</v>
+        <v>955.28</v>
       </c>
       <c r="L4" t="n">
-        <v>24314.46</v>
+        <v>22985.14</v>
       </c>
       <c r="M4" t="n">
-        <v>1941.5</v>
+        <v>1832.69</v>
       </c>
       <c r="N4" t="n">
-        <v>320.78</v>
+        <v>306.04</v>
       </c>
       <c r="O4" t="n">
-        <v>416.42</v>
+        <v>393.65</v>
       </c>
       <c r="P4" t="n">
-        <v>4858.18</v>
+        <v>4592.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>573.8200000000001</v>
+        <v>526.36</v>
       </c>
       <c r="R4" t="n">
         <v>2174.95</v>
       </c>
       <c r="S4" t="n">
-        <v>565.92</v>
+        <v>534.98</v>
       </c>
       <c r="T4" t="n">
-        <v>35166.03</v>
+        <v>33346.38</v>
       </c>
       <c r="U4" t="n">
-        <v>-12628.82</v>
+        <v>-11952.08</v>
       </c>
     </row>
     <row r="5">
@@ -759,58 +759,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>100841.18</v>
+        <v>82167.87</v>
       </c>
       <c r="E5" t="n">
         <v>13759.32</v>
       </c>
       <c r="F5" t="n">
-        <v>87081.86</v>
+        <v>68408.55</v>
       </c>
       <c r="G5" t="n">
-        <v>79352.66</v>
+        <v>65134.23</v>
       </c>
       <c r="H5" t="n">
-        <v>7729.2</v>
+        <v>3274.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0888</v>
+        <v>0.0479</v>
       </c>
       <c r="J5" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K5" t="n">
-        <v>750.71</v>
+        <v>645.36</v>
       </c>
       <c r="L5" t="n">
-        <v>20570.11</v>
+        <v>16761.03</v>
       </c>
       <c r="M5" t="n">
-        <v>1373.68</v>
+        <v>1124.61</v>
       </c>
       <c r="N5" t="n">
-        <v>237.97</v>
+        <v>195.11</v>
       </c>
       <c r="O5" t="n">
-        <v>302.52</v>
+        <v>246.5</v>
       </c>
       <c r="P5" t="n">
-        <v>3529.44</v>
+        <v>2875.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>496.2</v>
+        <v>453.42</v>
       </c>
       <c r="R5" t="n">
         <v>1742.83</v>
       </c>
       <c r="S5" t="n">
-        <v>578.38</v>
+        <v>471.28</v>
       </c>
       <c r="T5" t="n">
-        <v>28831.13</v>
+        <v>23870.66</v>
       </c>
       <c r="U5" t="n">
-        <v>-21101.93</v>
+        <v>-20596.34</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>153829.26</v>
+        <v>128570.96</v>
       </c>
       <c r="E6" t="n">
         <v>29987.69</v>
       </c>
       <c r="F6" t="n">
-        <v>123841.57</v>
+        <v>98583.27</v>
       </c>
       <c r="G6" t="n">
-        <v>118161.22</v>
+        <v>99329.55</v>
       </c>
       <c r="H6" t="n">
-        <v>5680.35</v>
+        <v>-746.28</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0459</v>
+        <v>-0.0076</v>
       </c>
       <c r="J6" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>917.34</v>
+        <v>821.53</v>
       </c>
       <c r="L6" t="n">
-        <v>21783.42</v>
+        <v>18206.65</v>
       </c>
       <c r="M6" t="n">
-        <v>2171.42</v>
+        <v>1793.23</v>
       </c>
       <c r="N6" t="n">
-        <v>356.33</v>
+        <v>297.94</v>
       </c>
       <c r="O6" t="n">
-        <v>461.49</v>
+        <v>385.71</v>
       </c>
       <c r="P6" t="n">
-        <v>5384.02</v>
+        <v>4499.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>583.64</v>
+        <v>518.79</v>
       </c>
       <c r="R6" t="n">
         <v>5115.44</v>
       </c>
       <c r="S6" t="n">
-        <v>733.58</v>
+        <v>613.13</v>
       </c>
       <c r="T6" t="n">
-        <v>36589.34</v>
+        <v>31430.87</v>
       </c>
       <c r="U6" t="n">
-        <v>-30908.99</v>
+        <v>-32177.15</v>
       </c>
     </row>
     <row r="7">
@@ -901,58 +901,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>137840.69</v>
+        <v>102127.01</v>
       </c>
       <c r="E7" t="n">
         <v>70.61</v>
       </c>
       <c r="F7" t="n">
-        <v>137770.08</v>
+        <v>102056.4</v>
       </c>
       <c r="G7" t="n">
-        <v>99312.63</v>
+        <v>73793.02</v>
       </c>
       <c r="H7" t="n">
-        <v>38457.45</v>
+        <v>28263.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2791</v>
+        <v>0.2769</v>
       </c>
       <c r="J7" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>1275.65</v>
+        <v>1214.96</v>
       </c>
       <c r="L7" t="n">
-        <v>23402.02</v>
+        <v>17338.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1936.16</v>
+        <v>1431.97</v>
       </c>
       <c r="N7" t="n">
-        <v>319.58</v>
+        <v>235.64</v>
       </c>
       <c r="O7" t="n">
-        <v>413.52</v>
+        <v>306.38</v>
       </c>
       <c r="P7" t="n">
-        <v>4824.42</v>
+        <v>3574.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>430.78</v>
+        <v>335.05</v>
       </c>
       <c r="R7" t="n">
         <v>13.26</v>
       </c>
       <c r="S7" t="n">
-        <v>653.08</v>
+        <v>483.87</v>
       </c>
       <c r="T7" t="n">
-        <v>31992.82</v>
+        <v>23719.32</v>
       </c>
       <c r="U7" t="n">
-        <v>6464.63</v>
+        <v>4544.06</v>
       </c>
     </row>
     <row r="8">
@@ -972,58 +972,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60998.78</v>
+        <v>47826.49</v>
       </c>
       <c r="E8" t="n">
         <v>4640.77</v>
       </c>
       <c r="F8" t="n">
-        <v>56358.01</v>
+        <v>43185.72</v>
       </c>
       <c r="G8" t="n">
-        <v>45317.01</v>
+        <v>35390.72</v>
       </c>
       <c r="H8" t="n">
-        <v>11041</v>
+        <v>7795</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1959</v>
+        <v>0.1805</v>
       </c>
       <c r="J8" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>569.27</v>
+        <v>583.59</v>
       </c>
       <c r="L8" t="n">
-        <v>2671.98</v>
+        <v>2094.98</v>
       </c>
       <c r="M8" t="n">
-        <v>790.67</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>163.92</v>
+        <v>125.85</v>
       </c>
       <c r="O8" t="n">
-        <v>183</v>
+        <v>143.48</v>
       </c>
       <c r="P8" t="n">
-        <v>2134.96</v>
+        <v>1673.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>290.93</v>
+        <v>217.46</v>
       </c>
       <c r="R8" t="n">
         <v>568.83</v>
       </c>
       <c r="S8" t="n">
-        <v>245.41</v>
+        <v>192.41</v>
       </c>
       <c r="T8" t="n">
-        <v>7049.7</v>
+        <v>5647.62</v>
       </c>
       <c r="U8" t="n">
-        <v>3991.3</v>
+        <v>2147.38</v>
       </c>
     </row>
     <row r="9">
@@ -1043,58 +1043,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59446.39</v>
+        <v>93650.14999999999</v>
       </c>
       <c r="E9" t="n">
         <v>5473.97</v>
       </c>
       <c r="F9" t="n">
-        <v>53972.42</v>
+        <v>88176.17999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>45186.39</v>
+        <v>70432.17999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>8786.030000000001</v>
+        <v>17744</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1628</v>
+        <v>0.2012</v>
       </c>
       <c r="J9" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="K9" t="n">
-        <v>539.72</v>
+        <v>558.08</v>
       </c>
       <c r="L9" t="n">
-        <v>2675.52</v>
+        <v>4214.94</v>
       </c>
       <c r="M9" t="n">
-        <v>784.63</v>
+        <v>1214.78</v>
       </c>
       <c r="N9" t="n">
-        <v>157.78</v>
+        <v>251.48</v>
       </c>
       <c r="O9" t="n">
-        <v>178.34</v>
+        <v>280.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2080.62</v>
+        <v>3277.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>256.93</v>
+        <v>405.95</v>
       </c>
       <c r="R9" t="n">
         <v>825.25</v>
       </c>
       <c r="S9" t="n">
-        <v>195.58</v>
+        <v>308.11</v>
       </c>
       <c r="T9" t="n">
-        <v>7154.65</v>
+        <v>10779.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1631.38</v>
+        <v>6964.78</v>
       </c>
     </row>
     <row r="10">
@@ -1114,58 +1114,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76644.49000000001</v>
+        <v>53522.75</v>
       </c>
       <c r="E10" t="n">
         <v>5430.2</v>
       </c>
       <c r="F10" t="n">
-        <v>71214.28999999999</v>
+        <v>48092.55</v>
       </c>
       <c r="G10" t="n">
-        <v>58027.88</v>
+        <v>40307.51</v>
       </c>
       <c r="H10" t="n">
-        <v>13186.41</v>
+        <v>7785.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1852</v>
+        <v>0.1619</v>
       </c>
       <c r="J10" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="K10" t="n">
-        <v>684.75</v>
+        <v>579.4299999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>4752.14</v>
+        <v>3318.54</v>
       </c>
       <c r="M10" t="n">
-        <v>1022.94</v>
+        <v>690</v>
       </c>
       <c r="N10" t="n">
-        <v>203.88</v>
+        <v>151.79</v>
       </c>
       <c r="O10" t="n">
-        <v>229.93</v>
+        <v>160.57</v>
       </c>
       <c r="P10" t="n">
-        <v>2682.56</v>
+        <v>1873.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>471.91</v>
+        <v>376.62</v>
       </c>
       <c r="R10" t="n">
         <v>685.5599999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>200.43</v>
+        <v>139.96</v>
       </c>
       <c r="T10" t="n">
-        <v>10249.35</v>
+        <v>7396.34</v>
       </c>
       <c r="U10" t="n">
-        <v>2937.06</v>
+        <v>388.7</v>
       </c>
     </row>
     <row r="11">
@@ -1185,58 +1185,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83065.94</v>
+        <v>69341.42</v>
       </c>
       <c r="E11" t="n">
         <v>12289</v>
       </c>
       <c r="F11" t="n">
-        <v>70776.94</v>
+        <v>57052.42</v>
       </c>
       <c r="G11" t="n">
-        <v>63167.3</v>
+        <v>52959.61</v>
       </c>
       <c r="H11" t="n">
-        <v>7609.64</v>
+        <v>4092.81</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1075</v>
+        <v>0.0717</v>
       </c>
       <c r="J11" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K11" t="n">
-        <v>561.72</v>
+        <v>582.17</v>
       </c>
       <c r="L11" t="n">
-        <v>3597.69</v>
+        <v>3003.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1094.29</v>
+        <v>918.99</v>
       </c>
       <c r="N11" t="n">
-        <v>212</v>
+        <v>170.18</v>
       </c>
       <c r="O11" t="n">
-        <v>249.2</v>
+        <v>208.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2907.31</v>
+        <v>2426.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>379.58</v>
+        <v>295.23</v>
       </c>
       <c r="R11" t="n">
         <v>2273.45</v>
       </c>
       <c r="S11" t="n">
-        <v>350.3</v>
+        <v>292.42</v>
       </c>
       <c r="T11" t="n">
-        <v>11063.82</v>
+        <v>9588.5</v>
       </c>
       <c r="U11" t="n">
-        <v>-3454.18</v>
+        <v>-5495.69</v>
       </c>
     </row>
     <row r="12">
@@ -1256,58 +1256,58 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69059.94</v>
+        <v>57295.77</v>
       </c>
       <c r="E12" t="n">
         <v>1989.85</v>
       </c>
       <c r="F12" t="n">
-        <v>67070.09</v>
+        <v>55305.92</v>
       </c>
       <c r="G12" t="n">
-        <v>50967.14</v>
+        <v>43239.35</v>
       </c>
       <c r="H12" t="n">
-        <v>16102.95</v>
+        <v>12066.57</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2401</v>
+        <v>0.2182</v>
       </c>
       <c r="J12" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="K12" t="n">
-        <v>598.84</v>
+        <v>643.09</v>
       </c>
       <c r="L12" t="n">
-        <v>3575.79</v>
+        <v>2966.66</v>
       </c>
       <c r="M12" t="n">
-        <v>871.48</v>
+        <v>755.92</v>
       </c>
       <c r="N12" t="n">
-        <v>184.95</v>
+        <v>147.32</v>
       </c>
       <c r="O12" t="n">
-        <v>207.18</v>
+        <v>171.89</v>
       </c>
       <c r="P12" t="n">
-        <v>2417.1</v>
+        <v>2005.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>383.34</v>
+        <v>294.35</v>
       </c>
       <c r="R12" t="n">
         <v>299.7</v>
       </c>
       <c r="S12" t="n">
-        <v>172.31</v>
+        <v>142.96</v>
       </c>
       <c r="T12" t="n">
-        <v>8111.85</v>
+        <v>6784.15</v>
       </c>
       <c r="U12" t="n">
-        <v>7991.1</v>
+        <v>5282.42</v>
       </c>
     </row>
     <row r="13">
@@ -1327,58 +1327,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>92806.34</v>
+        <v>120385.3</v>
       </c>
       <c r="E13" t="n">
         <v>711.35</v>
       </c>
       <c r="F13" t="n">
-        <v>92094.99000000001</v>
+        <v>119673.95</v>
       </c>
       <c r="G13" t="n">
-        <v>69879.55</v>
+        <v>90215.89999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>22215.44</v>
+        <v>29458.05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2412</v>
+        <v>0.2462</v>
       </c>
       <c r="J13" t="n">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="K13" t="n">
-        <v>885.53</v>
+        <v>819.6799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6856.4</v>
+        <v>8893.9</v>
       </c>
       <c r="M13" t="n">
-        <v>1182.98</v>
+        <v>1536.62</v>
       </c>
       <c r="N13" t="n">
-        <v>240.76</v>
+        <v>316.67</v>
       </c>
       <c r="O13" t="n">
-        <v>278.42</v>
+        <v>361.16</v>
       </c>
       <c r="P13" t="n">
-        <v>3248.22</v>
+        <v>4213.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>518.5</v>
+        <v>727.9</v>
       </c>
       <c r="R13" t="n">
         <v>96.11</v>
       </c>
       <c r="S13" t="n">
-        <v>473.67</v>
+        <v>614.4299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>12895.05</v>
+        <v>16760.28</v>
       </c>
       <c r="U13" t="n">
-        <v>9320.389999999999</v>
+        <v>12697.77</v>
       </c>
     </row>
     <row r="14">
@@ -1398,58 +1398,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>342945.31</v>
+        <v>308078.11</v>
       </c>
       <c r="E14" t="n">
         <v>22526.54</v>
       </c>
       <c r="F14" t="n">
-        <v>320418.77</v>
+        <v>285551.57</v>
       </c>
       <c r="G14" t="n">
-        <v>255824.17</v>
+        <v>231167.56</v>
       </c>
       <c r="H14" t="n">
-        <v>64594.6</v>
+        <v>54384.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2016</v>
+        <v>0.1905</v>
       </c>
       <c r="J14" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K14" t="n">
-        <v>825.8200000000001</v>
+        <v>737.86</v>
       </c>
       <c r="L14" t="n">
-        <v>57218.78</v>
+        <v>51401.36</v>
       </c>
       <c r="M14" t="n">
-        <v>17092.41</v>
+        <v>15501.01</v>
       </c>
       <c r="N14" t="n">
-        <v>7674.99</v>
+        <v>6881.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2057.67</v>
+        <v>1848.47</v>
       </c>
       <c r="P14" t="n">
-        <v>18861.99</v>
+        <v>16944.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1396.29</v>
+        <v>1392.69</v>
       </c>
       <c r="R14" t="n">
         <v>4500.18</v>
       </c>
       <c r="S14" t="n">
-        <v>754.88</v>
+        <v>678.13</v>
       </c>
       <c r="T14" t="n">
-        <v>109557.19</v>
+        <v>99147.53999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-44962.59</v>
+        <v>-44763.53</v>
       </c>
     </row>
     <row r="15">
@@ -1469,58 +1469,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>322519.53</v>
+        <v>364407.66</v>
       </c>
       <c r="E15" t="n">
         <v>19557.12</v>
       </c>
       <c r="F15" t="n">
-        <v>302962.41</v>
+        <v>344850.54</v>
       </c>
       <c r="G15" t="n">
-        <v>236480.41</v>
+        <v>270002.29</v>
       </c>
       <c r="H15" t="n">
-        <v>66482</v>
+        <v>74848.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2194</v>
+        <v>0.217</v>
       </c>
       <c r="J15" t="n">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="K15" t="n">
-        <v>912.54</v>
+        <v>971.41</v>
       </c>
       <c r="L15" t="n">
-        <v>41345.9</v>
+        <v>46715.81</v>
       </c>
       <c r="M15" t="n">
-        <v>16041.7</v>
+        <v>18121.1</v>
       </c>
       <c r="N15" t="n">
-        <v>7274.31</v>
+        <v>8262.379999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1935.12</v>
+        <v>2186.45</v>
       </c>
       <c r="P15" t="n">
-        <v>17738.57</v>
+        <v>20042.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>710.83</v>
+        <v>760.08</v>
       </c>
       <c r="R15" t="n">
         <v>3542.57</v>
       </c>
       <c r="S15" t="n">
-        <v>1445.29</v>
+        <v>1633</v>
       </c>
       <c r="T15" t="n">
-        <v>90034.28999999999</v>
+        <v>101263.81</v>
       </c>
       <c r="U15" t="n">
-        <v>-23552.29</v>
+        <v>-26415.56</v>
       </c>
     </row>
     <row r="16">
@@ -1540,58 +1540,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>348508.06</v>
+        <v>415467.82</v>
       </c>
       <c r="E16" t="n">
         <v>35288.02</v>
       </c>
       <c r="F16" t="n">
-        <v>313220.04</v>
+        <v>380179.8</v>
       </c>
       <c r="G16" t="n">
-        <v>262160.72</v>
+        <v>307675.1</v>
       </c>
       <c r="H16" t="n">
-        <v>51059.32</v>
+        <v>72504.7</v>
       </c>
       <c r="I16" t="n">
-        <v>0.163</v>
+        <v>0.1907</v>
       </c>
       <c r="J16" t="n">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="K16" t="n">
-        <v>813.5599999999999</v>
+        <v>925.01</v>
       </c>
       <c r="L16" t="n">
-        <v>57395.56</v>
+        <v>68423.12</v>
       </c>
       <c r="M16" t="n">
-        <v>17342.32</v>
+        <v>20529.84</v>
       </c>
       <c r="N16" t="n">
-        <v>7773.26</v>
+        <v>9299.370000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>2091.05</v>
+        <v>2492.81</v>
       </c>
       <c r="P16" t="n">
-        <v>19167.94</v>
+        <v>22850.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>1484.82</v>
+        <v>1585.09</v>
       </c>
       <c r="R16" t="n">
         <v>6670.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1319.85</v>
+        <v>1573.43</v>
       </c>
       <c r="T16" t="n">
-        <v>113244.9</v>
+        <v>133424.49</v>
       </c>
       <c r="U16" t="n">
-        <v>-62185.58</v>
+        <v>-60919.79</v>
       </c>
     </row>
     <row r="17">
@@ -1611,58 +1611,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>429427.6</v>
+        <v>464797.39</v>
       </c>
       <c r="E17" t="n">
         <v>38874.07</v>
       </c>
       <c r="F17" t="n">
-        <v>390553.53</v>
+        <v>425923.32</v>
       </c>
       <c r="G17" t="n">
-        <v>325160.58</v>
+        <v>349601.15</v>
       </c>
       <c r="H17" t="n">
-        <v>65392.95</v>
+        <v>76322.17</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1674</v>
+        <v>0.1792</v>
       </c>
       <c r="J17" t="n">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="K17" t="n">
-        <v>1047.06</v>
+        <v>1064.81</v>
       </c>
       <c r="L17" t="n">
-        <v>80079.84</v>
+        <v>86675.62</v>
       </c>
       <c r="M17" t="n">
-        <v>21053.61</v>
+        <v>22662.17</v>
       </c>
       <c r="N17" t="n">
-        <v>9707.889999999999</v>
+        <v>10512.31</v>
       </c>
       <c r="O17" t="n">
-        <v>2576.57</v>
+        <v>2788.78</v>
       </c>
       <c r="P17" t="n">
-        <v>23618.52</v>
+        <v>25563.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>1142.17</v>
+        <v>1224.84</v>
       </c>
       <c r="R17" t="n">
         <v>5988.98</v>
       </c>
       <c r="S17" t="n">
-        <v>2425.37</v>
+        <v>2625.14</v>
       </c>
       <c r="T17" t="n">
-        <v>146592.95</v>
+        <v>158041.7</v>
       </c>
       <c r="U17" t="n">
-        <v>-81200</v>
+        <v>-81719.53</v>
       </c>
     </row>
     <row r="18">
@@ -1682,58 +1682,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>380916.18</v>
+        <v>316019.46</v>
       </c>
       <c r="E18" t="n">
         <v>39365.02</v>
       </c>
       <c r="F18" t="n">
-        <v>341551.16</v>
+        <v>276654.44</v>
       </c>
       <c r="G18" t="n">
-        <v>284104.96</v>
+        <v>237835.02</v>
       </c>
       <c r="H18" t="n">
-        <v>57446.2</v>
+        <v>38819.42</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1682</v>
+        <v>0.1403</v>
       </c>
       <c r="J18" t="n">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="K18" t="n">
-        <v>962.12</v>
+        <v>944.21</v>
       </c>
       <c r="L18" t="n">
-        <v>66902.60000000001</v>
+        <v>55504.4</v>
       </c>
       <c r="M18" t="n">
-        <v>18643.6</v>
+        <v>15445.01</v>
       </c>
       <c r="N18" t="n">
-        <v>8692.959999999999</v>
+        <v>7252.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2285.5</v>
+        <v>1896.12</v>
       </c>
       <c r="P18" t="n">
-        <v>20950.39</v>
+        <v>17381.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>766.0700000000001</v>
+        <v>632.28</v>
       </c>
       <c r="R18" t="n">
         <v>5746.8</v>
       </c>
       <c r="S18" t="n">
-        <v>983.6900000000001</v>
+        <v>816.09</v>
       </c>
       <c r="T18" t="n">
-        <v>124971.61</v>
+        <v>104673.82</v>
       </c>
       <c r="U18" t="n">
-        <v>-67525.41</v>
+        <v>-65854.39999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1753,58 +1753,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>374915.23</v>
+        <v>330461.47</v>
       </c>
       <c r="E19" t="n">
         <v>1718.88</v>
       </c>
       <c r="F19" t="n">
-        <v>373196.35</v>
+        <v>328742.59</v>
       </c>
       <c r="G19" t="n">
-        <v>278153.29</v>
+        <v>245603.01</v>
       </c>
       <c r="H19" t="n">
-        <v>95043.06</v>
+        <v>83139.58</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2547</v>
+        <v>0.2529</v>
       </c>
       <c r="J19" t="n">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="K19" t="n">
-        <v>995.1900000000001</v>
+        <v>908.13</v>
       </c>
       <c r="L19" t="n">
-        <v>69154.13</v>
+        <v>60954.52</v>
       </c>
       <c r="M19" t="n">
-        <v>18487.29</v>
+        <v>16401.8</v>
       </c>
       <c r="N19" t="n">
-        <v>8420.59</v>
+        <v>7336.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2249.49</v>
+        <v>1982.77</v>
       </c>
       <c r="P19" t="n">
-        <v>20620.34</v>
+        <v>18175.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1021.61</v>
+        <v>986.2</v>
       </c>
       <c r="R19" t="n">
         <v>265.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1412.87</v>
+        <v>1245.35</v>
       </c>
       <c r="T19" t="n">
-        <v>121631.73</v>
+        <v>107347.92</v>
       </c>
       <c r="U19" t="n">
-        <v>-26588.67</v>
+        <v>-24208.34</v>
       </c>
     </row>
     <row r="20">
@@ -1824,58 +1824,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>197843.9</v>
+        <v>177374.86</v>
       </c>
       <c r="E20" t="n">
         <v>7952.89</v>
       </c>
       <c r="F20" t="n">
-        <v>189891.01</v>
+        <v>169421.97</v>
       </c>
       <c r="G20" t="n">
-        <v>146242.54</v>
+        <v>131272.85</v>
       </c>
       <c r="H20" t="n">
-        <v>43648.47</v>
+        <v>38149.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2299</v>
+        <v>0.2252</v>
       </c>
       <c r="J20" t="n">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K20" t="n">
-        <v>1150.85</v>
+        <v>1245.75</v>
       </c>
       <c r="L20" t="n">
-        <v>19155.25</v>
+        <v>17173.44</v>
       </c>
       <c r="M20" t="n">
-        <v>8431.57</v>
+        <v>7475.82</v>
       </c>
       <c r="N20" t="n">
-        <v>4468.63</v>
+        <v>4034.39</v>
       </c>
       <c r="O20" t="n">
-        <v>1187.06</v>
+        <v>1064.25</v>
       </c>
       <c r="P20" t="n">
-        <v>10881.41</v>
+        <v>9755.620000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>400.04</v>
+        <v>329.73</v>
       </c>
       <c r="R20" t="n">
         <v>1537.3</v>
       </c>
       <c r="S20" t="n">
-        <v>965.39</v>
+        <v>865.51</v>
       </c>
       <c r="T20" t="n">
-        <v>47026.65</v>
+        <v>42236.06</v>
       </c>
       <c r="U20" t="n">
-        <v>-3378.18</v>
+        <v>-4086.94</v>
       </c>
     </row>
     <row r="21">
@@ -1895,58 +1895,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>198033.29</v>
+        <v>327814.51</v>
       </c>
       <c r="E21" t="n">
         <v>20930.54</v>
       </c>
       <c r="F21" t="n">
-        <v>177102.75</v>
+        <v>306883.97</v>
       </c>
       <c r="G21" t="n">
-        <v>149395.48</v>
+        <v>246775.35</v>
       </c>
       <c r="H21" t="n">
-        <v>27707.27</v>
+        <v>60108.62</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1564</v>
+        <v>0.1959</v>
       </c>
       <c r="J21" t="n">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="K21" t="n">
-        <v>1150.02</v>
+        <v>1184.88</v>
       </c>
       <c r="L21" t="n">
-        <v>22560.12</v>
+        <v>37344.91</v>
       </c>
       <c r="M21" t="n">
-        <v>8520.959999999999</v>
+        <v>14012.01</v>
       </c>
       <c r="N21" t="n">
-        <v>4505.69</v>
+        <v>7433.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1188.2</v>
+        <v>1966.89</v>
       </c>
       <c r="P21" t="n">
-        <v>10891.83</v>
+        <v>18029.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>464.85</v>
+        <v>781.8</v>
       </c>
       <c r="R21" t="n">
         <v>3186.56</v>
       </c>
       <c r="S21" t="n">
-        <v>740.48</v>
+        <v>1225.75</v>
       </c>
       <c r="T21" t="n">
-        <v>52058.68</v>
+        <v>83980.97</v>
       </c>
       <c r="U21" t="n">
-        <v>-24351.41</v>
+        <v>-23872.35</v>
       </c>
     </row>
     <row r="22">
@@ -1966,43 +1966,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>230493.71</v>
+        <v>232747.28</v>
       </c>
       <c r="E22" t="n">
         <v>12579.44</v>
       </c>
       <c r="F22" t="n">
-        <v>217914.27</v>
+        <v>220167.84</v>
       </c>
       <c r="G22" t="n">
-        <v>170859.72</v>
+        <v>172920.54</v>
       </c>
       <c r="H22" t="n">
-        <v>47054.55</v>
+        <v>47247.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2159</v>
+        <v>0.2146</v>
       </c>
       <c r="J22" t="n">
         <v>159</v>
       </c>
       <c r="K22" t="n">
-        <v>1370.53</v>
+        <v>1384.7</v>
       </c>
       <c r="L22" t="n">
-        <v>22793.37</v>
+        <v>23016.22</v>
       </c>
       <c r="M22" t="n">
-        <v>9666.530000000001</v>
+        <v>9802.25</v>
       </c>
       <c r="N22" t="n">
-        <v>5253.16</v>
+        <v>5309.79</v>
       </c>
       <c r="O22" t="n">
-        <v>1382.96</v>
+        <v>1396.48</v>
       </c>
       <c r="P22" t="n">
-        <v>12677.15</v>
+        <v>12801.1</v>
       </c>
       <c r="Q22" t="n">
         <v>368.58</v>
@@ -2011,13 +2011,13 @@
         <v>1298.29</v>
       </c>
       <c r="S22" t="n">
-        <v>1205.55</v>
+        <v>1217.34</v>
       </c>
       <c r="T22" t="n">
-        <v>54645.59</v>
+        <v>55210.05</v>
       </c>
       <c r="U22" t="n">
-        <v>-7591.04</v>
+        <v>-7962.75</v>
       </c>
     </row>
     <row r="23">
@@ -2037,58 +2037,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>248058.62</v>
+        <v>180833.23</v>
       </c>
       <c r="E23" t="n">
         <v>13507.61</v>
       </c>
       <c r="F23" t="n">
-        <v>234551.01</v>
+        <v>167325.62</v>
       </c>
       <c r="G23" t="n">
-        <v>185555.01</v>
+        <v>134102.96</v>
       </c>
       <c r="H23" t="n">
-        <v>48996</v>
+        <v>33222.66</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2089</v>
+        <v>0.1986</v>
       </c>
       <c r="J23" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="K23" t="n">
-        <v>1465.94</v>
+        <v>1338.6</v>
       </c>
       <c r="L23" t="n">
-        <v>29004.1</v>
+        <v>21143.81</v>
       </c>
       <c r="M23" t="n">
-        <v>10440.15</v>
+        <v>7646.77</v>
       </c>
       <c r="N23" t="n">
-        <v>5668.44</v>
+        <v>4121.26</v>
       </c>
       <c r="O23" t="n">
-        <v>1488.35</v>
+        <v>1085</v>
       </c>
       <c r="P23" t="n">
-        <v>13643.22</v>
+        <v>9945.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>321.81</v>
+        <v>251.41</v>
       </c>
       <c r="R23" t="n">
         <v>2407.14</v>
       </c>
       <c r="S23" t="n">
-        <v>1117.78</v>
+        <v>814.86</v>
       </c>
       <c r="T23" t="n">
-        <v>64090.99</v>
+        <v>47416.08</v>
       </c>
       <c r="U23" t="n">
-        <v>-15094.99</v>
+        <v>-14193.42</v>
       </c>
     </row>
     <row r="24">
@@ -2108,58 +2108,58 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>194785.56</v>
+        <v>178104.94</v>
       </c>
       <c r="E24" t="n">
         <v>13981.57</v>
       </c>
       <c r="F24" t="n">
-        <v>180803.99</v>
+        <v>164123.37</v>
       </c>
       <c r="G24" t="n">
-        <v>147626.32</v>
+        <v>134759.36</v>
       </c>
       <c r="H24" t="n">
-        <v>33177.67</v>
+        <v>29364.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1835</v>
+        <v>0.1789</v>
       </c>
       <c r="J24" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K24" t="n">
-        <v>1109.23</v>
+        <v>1086.91</v>
       </c>
       <c r="L24" t="n">
-        <v>21302.11</v>
+        <v>19477.89</v>
       </c>
       <c r="M24" t="n">
-        <v>8449.99</v>
+        <v>7795.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4391.43</v>
+        <v>4003.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1168.71</v>
+        <v>1068.63</v>
       </c>
       <c r="P24" t="n">
-        <v>10713.21</v>
+        <v>9795.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>555.73</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="R24" t="n">
         <v>2424.51</v>
       </c>
       <c r="S24" t="n">
-        <v>520.34</v>
+        <v>475.78</v>
       </c>
       <c r="T24" t="n">
-        <v>49526.03</v>
+        <v>45556.25</v>
       </c>
       <c r="U24" t="n">
-        <v>-16348.36</v>
+        <v>-16192.24</v>
       </c>
     </row>
     <row r="25">
@@ -2179,58 +2179,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>162120.15</v>
+        <v>134460.41</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>162120.15</v>
+        <v>134460.41</v>
       </c>
       <c r="G25" t="n">
-        <v>122988.17</v>
+        <v>102836.18</v>
       </c>
       <c r="H25" t="n">
-        <v>39131.98</v>
+        <v>31624.23</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2414</v>
+        <v>0.2352</v>
       </c>
       <c r="J25" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="K25" t="n">
-        <v>1276.54</v>
+        <v>1372.05</v>
       </c>
       <c r="L25" t="n">
-        <v>19417.1</v>
+        <v>16104.3</v>
       </c>
       <c r="M25" t="n">
-        <v>6916.36</v>
+        <v>5693.26</v>
       </c>
       <c r="N25" t="n">
-        <v>3671.55</v>
+        <v>3056.82</v>
       </c>
       <c r="O25" t="n">
-        <v>972.72</v>
+        <v>806.76</v>
       </c>
       <c r="P25" t="n">
-        <v>8916.610000000001</v>
+        <v>7395.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>344.94</v>
+        <v>266.17</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>353.32</v>
+        <v>293.04</v>
       </c>
       <c r="T25" t="n">
-        <v>40592.6</v>
+        <v>33615.67</v>
       </c>
       <c r="U25" t="n">
-        <v>-1460.62</v>
+        <v>-1991.44</v>
       </c>
     </row>
     <row r="26">
@@ -2250,58 +2250,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>274450.65</v>
+        <v>231749.81</v>
       </c>
       <c r="E26" t="n">
         <v>31711.35</v>
       </c>
       <c r="F26" t="n">
-        <v>242739.3</v>
+        <v>200038.46</v>
       </c>
       <c r="G26" t="n">
-        <v>204247.25</v>
+        <v>173780.7</v>
       </c>
       <c r="H26" t="n">
-        <v>38492.05</v>
+        <v>26257.76</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1586</v>
+        <v>0.1313</v>
       </c>
       <c r="J26" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="K26" t="n">
-        <v>642.17</v>
+        <v>600.72</v>
       </c>
       <c r="L26" t="n">
-        <v>39303.38</v>
+        <v>33188.3</v>
       </c>
       <c r="M26" t="n">
-        <v>21485.13</v>
+        <v>17779.87</v>
       </c>
       <c r="N26" t="n">
-        <v>6892.16</v>
+        <v>5833</v>
       </c>
       <c r="O26" t="n">
-        <v>1646.7</v>
+        <v>1390.5</v>
       </c>
       <c r="P26" t="n">
-        <v>15094.79</v>
+        <v>12746.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>926.4299999999999</v>
+        <v>816.14</v>
       </c>
       <c r="R26" t="n">
         <v>6239.11</v>
       </c>
       <c r="S26" t="n">
-        <v>1343.81</v>
+        <v>1134.73</v>
       </c>
       <c r="T26" t="n">
-        <v>92931.50999999999</v>
+        <v>79127.89</v>
       </c>
       <c r="U26" t="n">
-        <v>-54439.46</v>
+        <v>-52870.13</v>
       </c>
     </row>
     <row r="27">
@@ -2321,58 +2321,58 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>235749.3</v>
+        <v>334218.78</v>
       </c>
       <c r="E27" t="n">
         <v>15406.49</v>
       </c>
       <c r="F27" t="n">
-        <v>220342.81</v>
+        <v>318812.29</v>
       </c>
       <c r="G27" t="n">
-        <v>172748.99</v>
+        <v>242724.19</v>
       </c>
       <c r="H27" t="n">
-        <v>47593.82</v>
+        <v>76088.10000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.216</v>
+        <v>0.2387</v>
       </c>
       <c r="J27" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
       <c r="K27" t="n">
-        <v>605.34</v>
+        <v>722.9299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>28432.48</v>
+        <v>40308.36</v>
       </c>
       <c r="M27" t="n">
-        <v>18400.96</v>
+        <v>26864.24</v>
       </c>
       <c r="N27" t="n">
-        <v>5890.55</v>
+        <v>8341.309999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>1414.5</v>
+        <v>2005.31</v>
       </c>
       <c r="P27" t="n">
-        <v>12966.21</v>
+        <v>18382.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>1196.24</v>
+        <v>1449.29</v>
       </c>
       <c r="R27" t="n">
         <v>1884.96</v>
       </c>
       <c r="S27" t="n">
-        <v>906.14</v>
+        <v>1284.62</v>
       </c>
       <c r="T27" t="n">
-        <v>71092.03999999999</v>
+        <v>100520.12</v>
       </c>
       <c r="U27" t="n">
-        <v>-23498.22</v>
+        <v>-24432.02</v>
       </c>
     </row>
     <row r="28">
@@ -2392,58 +2392,58 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>272179.95</v>
+        <v>282524.21</v>
       </c>
       <c r="E28" t="n">
         <v>23178.25</v>
       </c>
       <c r="F28" t="n">
-        <v>249001.7</v>
+        <v>259345.96</v>
       </c>
       <c r="G28" t="n">
-        <v>202344.89</v>
+        <v>208922.18</v>
       </c>
       <c r="H28" t="n">
-        <v>46656.81</v>
+        <v>50423.78</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1874</v>
+        <v>0.1944</v>
       </c>
       <c r="J28" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="K28" t="n">
-        <v>624.0599999999999</v>
+        <v>635.65</v>
       </c>
       <c r="L28" t="n">
-        <v>45229.12</v>
+        <v>46948.07</v>
       </c>
       <c r="M28" t="n">
-        <v>20476.89</v>
+        <v>21559.6</v>
       </c>
       <c r="N28" t="n">
-        <v>6857.49</v>
+        <v>7104.94</v>
       </c>
       <c r="O28" t="n">
-        <v>1633.08</v>
+        <v>1695.15</v>
       </c>
       <c r="P28" t="n">
-        <v>14969.9</v>
+        <v>15538.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>1508.55</v>
+        <v>1542.58</v>
       </c>
       <c r="R28" t="n">
         <v>2833.21</v>
       </c>
       <c r="S28" t="n">
-        <v>1292.97</v>
+        <v>1342.11</v>
       </c>
       <c r="T28" t="n">
-        <v>94801.2</v>
+        <v>98564.49000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-48144.39</v>
+        <v>-48140.71</v>
       </c>
     </row>
     <row r="29">
@@ -2463,58 +2463,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>256708.75</v>
+        <v>247079.07</v>
       </c>
       <c r="E29" t="n">
         <v>21244.2</v>
       </c>
       <c r="F29" t="n">
-        <v>235464.55</v>
+        <v>225834.87</v>
       </c>
       <c r="G29" t="n">
-        <v>192419.83</v>
+        <v>183947.11</v>
       </c>
       <c r="H29" t="n">
-        <v>43044.72</v>
+        <v>41887.76</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1828</v>
+        <v>0.1855</v>
       </c>
       <c r="J29" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K29" t="n">
-        <v>645.11</v>
+        <v>623.85</v>
       </c>
       <c r="L29" t="n">
-        <v>54003.3</v>
+        <v>51977.52</v>
       </c>
       <c r="M29" t="n">
-        <v>19956.16</v>
+        <v>18973.23</v>
       </c>
       <c r="N29" t="n">
-        <v>6426.17</v>
+        <v>6189.61</v>
       </c>
       <c r="O29" t="n">
-        <v>1540.25</v>
+        <v>1482.47</v>
       </c>
       <c r="P29" t="n">
-        <v>14118.98</v>
+        <v>13589.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>1824.29</v>
+        <v>1809.29</v>
       </c>
       <c r="R29" t="n">
         <v>3748.17</v>
       </c>
       <c r="S29" t="n">
-        <v>806.12</v>
+        <v>775.88</v>
       </c>
       <c r="T29" t="n">
-        <v>102423.44</v>
+        <v>98545.52</v>
       </c>
       <c r="U29" t="n">
-        <v>-59378.72</v>
+        <v>-56657.76</v>
       </c>
     </row>
     <row r="30">
@@ -2534,58 +2534,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>306008.6</v>
+        <v>301337.88</v>
       </c>
       <c r="E30" t="n">
         <v>19014.07</v>
       </c>
       <c r="F30" t="n">
-        <v>286994.53</v>
+        <v>282323.81</v>
       </c>
       <c r="G30" t="n">
-        <v>226911.9</v>
+        <v>226037.12</v>
       </c>
       <c r="H30" t="n">
-        <v>60082.63</v>
+        <v>56286.69</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2094</v>
+        <v>0.1994</v>
       </c>
       <c r="J30" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="K30" t="n">
-        <v>745.4400000000001</v>
+        <v>714.74</v>
       </c>
       <c r="L30" t="n">
-        <v>62344.89</v>
+        <v>61393.3</v>
       </c>
       <c r="M30" t="n">
-        <v>25218.87</v>
+        <v>24807.53</v>
       </c>
       <c r="N30" t="n">
-        <v>7633.04</v>
+        <v>7524.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1836.05</v>
+        <v>1808.03</v>
       </c>
       <c r="P30" t="n">
-        <v>16830.47</v>
+        <v>16573.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>1058.93</v>
+        <v>1086.43</v>
       </c>
       <c r="R30" t="n">
         <v>2074.65</v>
       </c>
       <c r="S30" t="n">
-        <v>905.77</v>
+        <v>891.9400000000001</v>
       </c>
       <c r="T30" t="n">
-        <v>117902.66</v>
+        <v>116160.24</v>
       </c>
       <c r="U30" t="n">
-        <v>-57820.03</v>
+        <v>-59873.55</v>
       </c>
     </row>
     <row r="31">
@@ -2605,58 +2605,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>336111.99</v>
+        <v>284299.49</v>
       </c>
       <c r="E31" t="n">
         <v>6688.04</v>
       </c>
       <c r="F31" t="n">
-        <v>329423.95</v>
+        <v>277611.45</v>
       </c>
       <c r="G31" t="n">
-        <v>245047.54</v>
+        <v>208309.1</v>
       </c>
       <c r="H31" t="n">
-        <v>84376.41</v>
+        <v>69302.35000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2561</v>
+        <v>0.2496</v>
       </c>
       <c r="J31" t="n">
-        <v>371</v>
+        <v>323</v>
       </c>
       <c r="K31" t="n">
-        <v>887.9400000000001</v>
+        <v>859.48</v>
       </c>
       <c r="L31" t="n">
-        <v>56825.65</v>
+        <v>48065.84</v>
       </c>
       <c r="M31" t="n">
-        <v>27362.89</v>
+        <v>22916.43</v>
       </c>
       <c r="N31" t="n">
-        <v>8384.99</v>
+        <v>7090.76</v>
       </c>
       <c r="O31" t="n">
-        <v>2016.67</v>
+        <v>1705.8</v>
       </c>
       <c r="P31" t="n">
-        <v>18486.16</v>
+        <v>15636.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>913.5</v>
+        <v>795.3099999999999</v>
       </c>
       <c r="R31" t="n">
         <v>1067.74</v>
       </c>
       <c r="S31" t="n">
-        <v>1010.41</v>
+        <v>854.65</v>
       </c>
       <c r="T31" t="n">
-        <v>116068.01</v>
+        <v>98133</v>
       </c>
       <c r="U31" t="n">
-        <v>-31691.6</v>
+        <v>-28830.65</v>
       </c>
     </row>
     <row r="32">
@@ -2676,58 +2676,58 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29699.94</v>
+        <v>44149.96</v>
       </c>
       <c r="E32" t="n">
         <v>1266.54</v>
       </c>
       <c r="F32" t="n">
-        <v>28433.4</v>
+        <v>42883.42</v>
       </c>
       <c r="G32" t="n">
-        <v>21648.15</v>
+        <v>32365.82</v>
       </c>
       <c r="H32" t="n">
-        <v>6785.25</v>
+        <v>10517.6</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2386</v>
+        <v>0.2453</v>
       </c>
       <c r="J32" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="K32" t="n">
-        <v>240.96</v>
+        <v>264.71</v>
       </c>
       <c r="L32" t="n">
-        <v>2832.09</v>
+        <v>4210</v>
       </c>
       <c r="M32" t="n">
-        <v>1466</v>
+        <v>2207.91</v>
       </c>
       <c r="N32" t="n">
-        <v>269.27</v>
+        <v>404.87</v>
       </c>
       <c r="O32" t="n">
-        <v>148.5</v>
+        <v>220.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2672.99</v>
+        <v>3973.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>334.1</v>
+        <v>458.68</v>
       </c>
       <c r="R32" t="n">
         <v>214.62</v>
       </c>
       <c r="S32" t="n">
-        <v>172.5</v>
+        <v>256.43</v>
       </c>
       <c r="T32" t="n">
-        <v>8110.07</v>
+        <v>11946.76</v>
       </c>
       <c r="U32" t="n">
-        <v>-1324.82</v>
+        <v>-1429.16</v>
       </c>
     </row>
     <row r="33">
@@ -2747,58 +2747,58 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29507.01</v>
+        <v>41958.9</v>
       </c>
       <c r="E33" t="n">
         <v>1737.43</v>
       </c>
       <c r="F33" t="n">
-        <v>27769.58</v>
+        <v>40221.47</v>
       </c>
       <c r="G33" t="n">
-        <v>21807.5</v>
+        <v>31161.4</v>
       </c>
       <c r="H33" t="n">
-        <v>5962.08</v>
+        <v>9060.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2147</v>
+        <v>0.2253</v>
       </c>
       <c r="J33" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="K33" t="n">
-        <v>241.47</v>
+        <v>229.84</v>
       </c>
       <c r="L33" t="n">
-        <v>2507.73</v>
+        <v>3565.98</v>
       </c>
       <c r="M33" t="n">
-        <v>1524.05</v>
+        <v>2181.22</v>
       </c>
       <c r="N33" t="n">
-        <v>265.49</v>
+        <v>387.91</v>
       </c>
       <c r="O33" t="n">
-        <v>147.54</v>
+        <v>209.79</v>
       </c>
       <c r="P33" t="n">
-        <v>2655.63</v>
+        <v>3776.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>278.28</v>
+        <v>423.46</v>
       </c>
       <c r="R33" t="n">
         <v>317.03</v>
       </c>
       <c r="S33" t="n">
-        <v>125.85</v>
+        <v>178.96</v>
       </c>
       <c r="T33" t="n">
-        <v>7821.59</v>
+        <v>11040.65</v>
       </c>
       <c r="U33" t="n">
-        <v>-1859.51</v>
+        <v>-1980.58</v>
       </c>
     </row>
     <row r="34">
@@ -2818,58 +2818,58 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>39417.57</v>
+        <v>35778.85</v>
       </c>
       <c r="E34" t="n">
         <v>3329.57</v>
       </c>
       <c r="F34" t="n">
-        <v>36088</v>
+        <v>32449.28</v>
       </c>
       <c r="G34" t="n">
-        <v>29537.78</v>
+        <v>26761.79</v>
       </c>
       <c r="H34" t="n">
-        <v>6550.22</v>
+        <v>5687.49</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1815</v>
+        <v>0.1753</v>
       </c>
       <c r="J34" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="K34" t="n">
-        <v>308.44</v>
+        <v>327.77</v>
       </c>
       <c r="L34" t="n">
-        <v>2488.35</v>
+        <v>2258.65</v>
       </c>
       <c r="M34" t="n">
-        <v>2050.61</v>
+        <v>1863.92</v>
       </c>
       <c r="N34" t="n">
-        <v>377.57</v>
+        <v>343.77</v>
       </c>
       <c r="O34" t="n">
-        <v>197.09</v>
+        <v>178.89</v>
       </c>
       <c r="P34" t="n">
-        <v>3547.58</v>
+        <v>3220.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>502.97</v>
+        <v>425.59</v>
       </c>
       <c r="R34" t="n">
         <v>555.37</v>
       </c>
       <c r="S34" t="n">
-        <v>234.2</v>
+        <v>212.58</v>
       </c>
       <c r="T34" t="n">
-        <v>9953.74</v>
+        <v>9058.870000000001</v>
       </c>
       <c r="U34" t="n">
-        <v>-3403.52</v>
+        <v>-3371.38</v>
       </c>
     </row>
     <row r="35">
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34474.15</v>
+        <v>28968.49</v>
       </c>
       <c r="E35" t="n">
         <v>4843.05</v>
       </c>
       <c r="F35" t="n">
-        <v>29631.1</v>
+        <v>24125.44</v>
       </c>
       <c r="G35" t="n">
-        <v>25117.03</v>
+        <v>20866.03</v>
       </c>
       <c r="H35" t="n">
-        <v>4514.07</v>
+        <v>3259.41</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1523</v>
+        <v>0.1351</v>
       </c>
       <c r="J35" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
-        <v>226.19</v>
+        <v>227.6</v>
       </c>
       <c r="L35" t="n">
-        <v>3754.42</v>
+        <v>3154.82</v>
       </c>
       <c r="M35" t="n">
-        <v>1734.95</v>
+        <v>1449.44</v>
       </c>
       <c r="N35" t="n">
-        <v>343.83</v>
+        <v>291.12</v>
       </c>
       <c r="O35" t="n">
-        <v>172.37</v>
+        <v>144.84</v>
       </c>
       <c r="P35" t="n">
-        <v>3102.67</v>
+        <v>2607.16</v>
       </c>
       <c r="Q35" t="n">
-        <v>551.98</v>
+        <v>446.64</v>
       </c>
       <c r="R35" t="n">
         <v>499.62</v>
       </c>
       <c r="S35" t="n">
-        <v>193.95</v>
+        <v>162.98</v>
       </c>
       <c r="T35" t="n">
-        <v>10353.8</v>
+        <v>8756.620000000001</v>
       </c>
       <c r="U35" t="n">
-        <v>-5839.73</v>
+        <v>-5497.21</v>
       </c>
     </row>
     <row r="36">
@@ -2960,58 +2960,58 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>69467.09</v>
+        <v>58119.96</v>
       </c>
       <c r="E36" t="n">
         <v>2823.74</v>
       </c>
       <c r="F36" t="n">
-        <v>66643.35000000001</v>
+        <v>55296.22</v>
       </c>
       <c r="G36" t="n">
-        <v>54796.08</v>
+        <v>46088.55</v>
       </c>
       <c r="H36" t="n">
-        <v>11847.27</v>
+        <v>9207.67</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1778</v>
+        <v>0.1665</v>
       </c>
       <c r="J36" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K36" t="n">
-        <v>490.02</v>
+        <v>526.63</v>
       </c>
       <c r="L36" t="n">
-        <v>5631.21</v>
+        <v>4711.38</v>
       </c>
       <c r="M36" t="n">
-        <v>3766.36</v>
+        <v>3164.41</v>
       </c>
       <c r="N36" t="n">
-        <v>710.4400000000001</v>
+        <v>593.54</v>
       </c>
       <c r="O36" t="n">
-        <v>347.34</v>
+        <v>290.6</v>
       </c>
       <c r="P36" t="n">
-        <v>6252.04</v>
+        <v>5230.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>660.25</v>
+        <v>509.75</v>
       </c>
       <c r="R36" t="n">
         <v>543.02</v>
       </c>
       <c r="S36" t="n">
-        <v>342.29</v>
+        <v>286.38</v>
       </c>
       <c r="T36" t="n">
-        <v>18252.95</v>
+        <v>15329.88</v>
       </c>
       <c r="U36" t="n">
-        <v>-6405.68</v>
+        <v>-6122.21</v>
       </c>
     </row>
     <row r="37">
@@ -3031,58 +3031,58 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>50595.19</v>
+        <v>44184.79</v>
       </c>
       <c r="E37" t="n">
         <v>800.61</v>
       </c>
       <c r="F37" t="n">
-        <v>49794.58</v>
+        <v>43384.18</v>
       </c>
       <c r="G37" t="n">
-        <v>37285.78</v>
+        <v>32948.73</v>
       </c>
       <c r="H37" t="n">
-        <v>12508.8</v>
+        <v>10435.45</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2512</v>
+        <v>0.2405</v>
       </c>
       <c r="J37" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="K37" t="n">
-        <v>433</v>
+        <v>510.4</v>
       </c>
       <c r="L37" t="n">
-        <v>3058.11</v>
+        <v>2670.65</v>
       </c>
       <c r="M37" t="n">
-        <v>2741.65</v>
+        <v>2416.71</v>
       </c>
       <c r="N37" t="n">
-        <v>504.98</v>
+        <v>450.36</v>
       </c>
       <c r="O37" t="n">
-        <v>252.98</v>
+        <v>220.92</v>
       </c>
       <c r="P37" t="n">
-        <v>4553.57</v>
+        <v>3976.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>435.49</v>
+        <v>321.89</v>
       </c>
       <c r="R37" t="n">
         <v>101.08</v>
       </c>
       <c r="S37" t="n">
-        <v>184.72</v>
+        <v>161.32</v>
       </c>
       <c r="T37" t="n">
-        <v>11832.58</v>
+        <v>10319.56</v>
       </c>
       <c r="U37" t="n">
-        <v>676.22</v>
+        <v>115.89</v>
       </c>
     </row>
   </sheetData>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>5906.07</v>
+        <v>8935.59</v>
       </c>
       <c r="F2" t="n">
-        <v>155557</v>
+        <v>235351</v>
       </c>
       <c r="G2" t="n">
-        <v>5098</v>
+        <v>7713</v>
       </c>
       <c r="H2" t="n">
-        <v>475</v>
+        <v>720</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>9729.48</v>
+        <v>14758.79</v>
       </c>
       <c r="K2" t="n">
         <v>1.65</v>
@@ -3213,22 +3213,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4149.66</v>
+        <v>6278.23</v>
       </c>
       <c r="F3" t="n">
-        <v>107964</v>
+        <v>163344</v>
       </c>
       <c r="G3" t="n">
-        <v>2855</v>
+        <v>4320</v>
       </c>
       <c r="H3" t="n">
-        <v>360</v>
+        <v>545</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>9783.76</v>
+        <v>14841.13</v>
       </c>
       <c r="K3" t="n">
         <v>2.36</v>
@@ -3254,22 +3254,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5358.05</v>
+        <v>8106.46</v>
       </c>
       <c r="F4" t="n">
-        <v>202104</v>
+        <v>305773</v>
       </c>
       <c r="G4" t="n">
-        <v>6532</v>
+        <v>9883</v>
       </c>
       <c r="H4" t="n">
-        <v>720</v>
+        <v>1089</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>10328.9</v>
+        <v>15668.06</v>
       </c>
       <c r="K4" t="n">
         <v>1.93</v>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>4438.83</v>
+        <v>6715.72</v>
       </c>
       <c r="F5" t="n">
-        <v>216739</v>
+        <v>327915</v>
       </c>
       <c r="G5" t="n">
-        <v>6206</v>
+        <v>9390</v>
       </c>
       <c r="H5" t="n">
-        <v>421</v>
+        <v>637</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>9766.34</v>
+        <v>14814.72</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6">
@@ -3328,22 +3328,22 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>6553.96</v>
+        <v>9915.84</v>
       </c>
       <c r="F6" t="n">
-        <v>169388</v>
+        <v>256277</v>
       </c>
       <c r="G6" t="n">
-        <v>4700</v>
+        <v>7112</v>
       </c>
       <c r="H6" t="n">
-        <v>391</v>
+        <v>592</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>10205.63</v>
+        <v>15481.08</v>
       </c>
       <c r="K6" t="n">
         <v>1.56</v>
@@ -3369,25 +3369,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4160.25</v>
+        <v>5179.27</v>
       </c>
       <c r="F7" t="n">
-        <v>171808</v>
+        <v>213891</v>
       </c>
       <c r="G7" t="n">
-        <v>4199</v>
+        <v>5227</v>
       </c>
       <c r="H7" t="n">
-        <v>551</v>
+        <v>686</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>7139.32</v>
+        <v>9386.85</v>
       </c>
       <c r="K7" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="8">
@@ -3410,25 +3410,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4099.42</v>
+        <v>5103.54</v>
       </c>
       <c r="F8" t="n">
-        <v>213353</v>
+        <v>265612</v>
       </c>
       <c r="G8" t="n">
-        <v>4985</v>
+        <v>6206</v>
       </c>
       <c r="H8" t="n">
-        <v>462</v>
+        <v>576</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>6637.58</v>
+        <v>8727.16</v>
       </c>
       <c r="K8" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="9">
@@ -3451,25 +3451,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7183.68</v>
+        <v>8943.27</v>
       </c>
       <c r="F9" t="n">
-        <v>353114</v>
+        <v>439607</v>
       </c>
       <c r="G9" t="n">
-        <v>3853</v>
+        <v>4797</v>
       </c>
       <c r="H9" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>6983.36</v>
+        <v>9181.790000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
@@ -3488,25 +3488,25 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>5158.19</v>
+        <v>6421.64</v>
       </c>
       <c r="F10" t="n">
-        <v>132821</v>
+        <v>165355</v>
       </c>
       <c r="G10" t="n">
-        <v>3187</v>
+        <v>3968</v>
       </c>
       <c r="H10" t="n">
-        <v>485</v>
+        <v>604</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>6831.68</v>
+        <v>8982.35</v>
       </c>
       <c r="K10" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -3525,25 +3525,25 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>6353.93</v>
+        <v>7910.27</v>
       </c>
       <c r="F11" t="n">
-        <v>309784</v>
+        <v>385663</v>
       </c>
       <c r="G11" t="n">
-        <v>4921</v>
+        <v>6127</v>
       </c>
       <c r="H11" t="n">
-        <v>792</v>
+        <v>987</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>6804.78</v>
+        <v>8946.99</v>
       </c>
       <c r="K11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="12">
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3847.87</v>
+        <v>3637.5</v>
       </c>
       <c r="F12" t="n">
-        <v>200265</v>
+        <v>189316</v>
       </c>
       <c r="G12" t="n">
-        <v>3850</v>
+        <v>3639</v>
       </c>
       <c r="H12" t="n">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>8099.78</v>
+        <v>8347.280000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -3607,25 +3607,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4239.92</v>
+        <v>4008.12</v>
       </c>
       <c r="F13" t="n">
-        <v>242960</v>
+        <v>229677</v>
       </c>
       <c r="G13" t="n">
-        <v>4853</v>
+        <v>4587</v>
       </c>
       <c r="H13" t="n">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>8739.879999999999</v>
+        <v>9006.940000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14">
@@ -3648,25 +3648,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5596.43</v>
+        <v>5290.47</v>
       </c>
       <c r="F14" t="n">
-        <v>151672</v>
+        <v>143380</v>
       </c>
       <c r="G14" t="n">
-        <v>2590</v>
+        <v>2449</v>
       </c>
       <c r="H14" t="n">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>8152.12</v>
+        <v>8401.219999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="15">
@@ -3689,25 +3689,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5042.81</v>
+        <v>4767.11</v>
       </c>
       <c r="F15" t="n">
-        <v>207977</v>
+        <v>196606</v>
       </c>
       <c r="G15" t="n">
-        <v>3617</v>
+        <v>3419</v>
       </c>
       <c r="H15" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>8755.43</v>
+        <v>9022.969999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="16">
@@ -3726,25 +3726,25 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>5587.43</v>
+        <v>5281.94</v>
       </c>
       <c r="F16" t="n">
-        <v>221563</v>
+        <v>209449</v>
       </c>
       <c r="G16" t="n">
-        <v>3956</v>
+        <v>3740</v>
       </c>
       <c r="H16" t="n">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>8337.950000000001</v>
+        <v>8592.73</v>
       </c>
       <c r="K16" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="17">
@@ -3767,25 +3767,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4369.19</v>
+        <v>3560.12</v>
       </c>
       <c r="F17" t="n">
-        <v>152743</v>
+        <v>124458</v>
       </c>
       <c r="G17" t="n">
-        <v>1235</v>
+        <v>1006</v>
       </c>
       <c r="H17" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="I17" t="n">
         <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>7046.65</v>
+        <v>6283.47</v>
       </c>
       <c r="K17" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="18">
@@ -3804,25 +3804,25 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>3165.78</v>
+        <v>2579.55</v>
       </c>
       <c r="F18" t="n">
-        <v>81058</v>
+        <v>66048</v>
       </c>
       <c r="G18" t="n">
-        <v>1514</v>
+        <v>1234</v>
       </c>
       <c r="H18" t="n">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="I18" t="n">
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>6870.13</v>
+        <v>6126.08</v>
       </c>
       <c r="K18" t="n">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="19">
@@ -3845,25 +3845,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3791.31</v>
+        <v>3089.25</v>
       </c>
       <c r="F19" t="n">
-        <v>183094</v>
+        <v>149189</v>
       </c>
       <c r="G19" t="n">
-        <v>3803</v>
+        <v>3098</v>
       </c>
       <c r="H19" t="n">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="I19" t="n">
         <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>7064.69</v>
+        <v>6299.57</v>
       </c>
       <c r="K19" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="20">
@@ -3886,25 +3886,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4290.05</v>
+        <v>3495.64</v>
       </c>
       <c r="F20" t="n">
-        <v>252479</v>
+        <v>205726</v>
       </c>
       <c r="G20" t="n">
-        <v>5377</v>
+        <v>4381</v>
       </c>
       <c r="H20" t="n">
-        <v>601</v>
+        <v>490</v>
       </c>
       <c r="I20" t="n">
         <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>6876.44</v>
+        <v>6131.7</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="21">
@@ -3927,25 +3927,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4953.78</v>
+        <v>4036.47</v>
       </c>
       <c r="F21" t="n">
-        <v>142267</v>
+        <v>115922</v>
       </c>
       <c r="G21" t="n">
-        <v>4842</v>
+        <v>3945</v>
       </c>
       <c r="H21" t="n">
-        <v>616</v>
+        <v>502</v>
       </c>
       <c r="I21" t="n">
         <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>7143.97</v>
+        <v>6370.25</v>
       </c>
       <c r="K21" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="22">
@@ -3968,25 +3968,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5236.3</v>
+        <v>4376.51</v>
       </c>
       <c r="F22" t="n">
-        <v>236912</v>
+        <v>198012</v>
       </c>
       <c r="G22" t="n">
-        <v>7203</v>
+        <v>6020</v>
       </c>
       <c r="H22" t="n">
-        <v>708</v>
+        <v>591</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>13096.35</v>
+        <v>11194.65</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="23">
@@ -4000,30 +4000,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>项目12</t>
+          <t>项目13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>4230.73</v>
+        <v>3536.06</v>
       </c>
       <c r="F23" t="n">
-        <v>172797</v>
+        <v>144424</v>
       </c>
       <c r="G23" t="n">
-        <v>3421</v>
+        <v>2859</v>
       </c>
       <c r="H23" t="n">
-        <v>367</v>
+        <v>307</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>12318.48</v>
+        <v>10529.74</v>
       </c>
       <c r="K23" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="24">
@@ -4046,25 +4046,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3171.65</v>
+        <v>2650.88</v>
       </c>
       <c r="F24" t="n">
-        <v>103892</v>
+        <v>86833</v>
       </c>
       <c r="G24" t="n">
-        <v>2562</v>
+        <v>2142</v>
       </c>
       <c r="H24" t="n">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>12668.45</v>
+        <v>10828.89</v>
       </c>
       <c r="K24" t="n">
-        <v>3.99</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="25">
@@ -4087,25 +4087,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3933.11</v>
+        <v>3287.3</v>
       </c>
       <c r="F25" t="n">
-        <v>181730</v>
+        <v>151890</v>
       </c>
       <c r="G25" t="n">
-        <v>4735</v>
+        <v>3957</v>
       </c>
       <c r="H25" t="n">
-        <v>403</v>
+        <v>336</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>12791.07</v>
+        <v>10933.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="26">
@@ -4128,25 +4128,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5211.63</v>
+        <v>4355.9</v>
       </c>
       <c r="F26" t="n">
-        <v>323523</v>
+        <v>270402</v>
       </c>
       <c r="G26" t="n">
-        <v>2697</v>
+        <v>2254</v>
       </c>
       <c r="H26" t="n">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>12750.82</v>
+        <v>10899.29</v>
       </c>
       <c r="K26" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>4900.72</v>
+        <v>3630.97</v>
       </c>
       <c r="F27" t="n">
-        <v>174514</v>
+        <v>129298</v>
       </c>
       <c r="G27" t="n">
-        <v>5407</v>
+        <v>4006</v>
       </c>
       <c r="H27" t="n">
-        <v>545</v>
+        <v>404</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>7583.34</v>
+        <v>6019.89</v>
       </c>
       <c r="K27" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="28">
@@ -4202,25 +4202,25 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>5140.6</v>
+        <v>3808.7</v>
       </c>
       <c r="F28" t="n">
-        <v>147003</v>
+        <v>108915</v>
       </c>
       <c r="G28" t="n">
-        <v>4497</v>
+        <v>3331</v>
       </c>
       <c r="H28" t="n">
-        <v>465</v>
+        <v>345</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>7418.84</v>
+        <v>5889.31</v>
       </c>
       <c r="K28" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="29">
@@ -4239,25 +4239,25 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>4518.38</v>
+        <v>3347.7</v>
       </c>
       <c r="F29" t="n">
-        <v>224296</v>
+        <v>166183</v>
       </c>
       <c r="G29" t="n">
-        <v>6260</v>
+        <v>4638</v>
       </c>
       <c r="H29" t="n">
-        <v>526</v>
+        <v>390</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>7960.2</v>
+        <v>6319.05</v>
       </c>
       <c r="K29" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="30">
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>4542.32</v>
+        <v>3365.43</v>
       </c>
       <c r="F30" t="n">
-        <v>146707</v>
+        <v>108696</v>
       </c>
       <c r="G30" t="n">
-        <v>4848</v>
+        <v>3592</v>
       </c>
       <c r="H30" t="n">
-        <v>511</v>
+        <v>379</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>7738.09</v>
+        <v>6142.74</v>
       </c>
       <c r="K30" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="31">
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>4300</v>
+        <v>3185.9</v>
       </c>
       <c r="F31" t="n">
-        <v>161119</v>
+        <v>119374</v>
       </c>
       <c r="G31" t="n">
-        <v>1835</v>
+        <v>1359</v>
       </c>
       <c r="H31" t="n">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>7325.58</v>
+        <v>5815.27</v>
       </c>
       <c r="K31" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="32">
@@ -4350,25 +4350,25 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>483.71</v>
+        <v>379.26</v>
       </c>
       <c r="F32" t="n">
-        <v>20240</v>
+        <v>15869</v>
       </c>
       <c r="G32" t="n">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="H32" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>1838.98</v>
+        <v>1285.98</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="33">
@@ -4387,16 +4387,16 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>494.75</v>
+        <v>387.91</v>
       </c>
       <c r="F33" t="n">
-        <v>14233</v>
+        <v>11160</v>
       </c>
       <c r="G33" t="n">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -4424,25 +4424,25 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>574.5599999999999</v>
+        <v>450.49</v>
       </c>
       <c r="F34" t="n">
-        <v>20087</v>
+        <v>15750</v>
       </c>
       <c r="G34" t="n">
-        <v>448</v>
+        <v>351</v>
       </c>
       <c r="H34" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>3772</v>
+        <v>3297.14</v>
       </c>
       <c r="K34" t="n">
-        <v>6.57</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="35">
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>542.04</v>
+        <v>424.99</v>
       </c>
       <c r="F35" t="n">
-        <v>14249</v>
+        <v>11172</v>
       </c>
       <c r="G35" t="n">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>1877.28</v>
+        <v>1312.76</v>
       </c>
       <c r="K35" t="n">
-        <v>3.46</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="36">
@@ -4493,30 +4493,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>项目14</t>
+          <t>项目15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>576.92</v>
+        <v>452.33</v>
       </c>
       <c r="F36" t="n">
-        <v>16188</v>
+        <v>12692</v>
       </c>
       <c r="G36" t="n">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="H36" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>1757.27</v>
+        <v>1843.25</v>
       </c>
       <c r="K36" t="n">
-        <v>3.05</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="37">
@@ -4535,25 +4535,25 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>577.36</v>
+        <v>909.55</v>
       </c>
       <c r="F37" t="n">
-        <v>15993</v>
+        <v>25196</v>
       </c>
       <c r="G37" t="n">
-        <v>415</v>
+        <v>654</v>
       </c>
       <c r="H37" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>3074.23</v>
+        <v>4904.38</v>
       </c>
       <c r="K37" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="38">
@@ -4572,25 +4572,25 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>579.01</v>
+        <v>912.15</v>
       </c>
       <c r="F38" t="n">
-        <v>15651</v>
+        <v>24656</v>
       </c>
       <c r="G38" t="n">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>1174.06</v>
+        <v>1755.93</v>
       </c>
       <c r="K38" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="39">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>630.77</v>
+        <v>993.6900000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>32533</v>
+        <v>51252</v>
       </c>
       <c r="G39" t="n">
-        <v>530</v>
+        <v>836</v>
       </c>
       <c r="H39" t="n">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>2976.93</v>
+        <v>4749.15</v>
       </c>
       <c r="K39" t="n">
-        <v>4.72</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="40">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>项目13</t>
+          <t>项目14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4654,25 +4654,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>409.46</v>
+        <v>645.05</v>
       </c>
       <c r="F40" t="n">
-        <v>14490</v>
+        <v>22827</v>
       </c>
       <c r="G40" t="n">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="H40" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>2986.67</v>
+        <v>4764.69</v>
       </c>
       <c r="K40" t="n">
-        <v>7.29</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="41">
@@ -4695,25 +4695,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>478.92</v>
+        <v>754.5</v>
       </c>
       <c r="F41" t="n">
-        <v>12108</v>
+        <v>19076</v>
       </c>
       <c r="G41" t="n">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="H41" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>3001.1</v>
+        <v>4787.7</v>
       </c>
       <c r="K41" t="n">
-        <v>6.27</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="42">
@@ -4732,25 +4732,25 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>758.1</v>
+        <v>529.4</v>
       </c>
       <c r="F42" t="n">
-        <v>19376</v>
+        <v>13531</v>
       </c>
       <c r="G42" t="n">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="H42" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2170.01</v>
+        <v>1265.84</v>
       </c>
       <c r="K42" t="n">
-        <v>2.86</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="43">
@@ -4769,25 +4769,25 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>984.5</v>
+        <v>687.5</v>
       </c>
       <c r="F43" t="n">
-        <v>36968</v>
+        <v>25815</v>
       </c>
       <c r="G43" t="n">
-        <v>1003</v>
+        <v>700</v>
       </c>
       <c r="H43" t="n">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>5278.53</v>
+        <v>3958.91</v>
       </c>
       <c r="K43" t="n">
-        <v>5.36</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="44">
@@ -4806,25 +4806,25 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>811.4400000000001</v>
+        <v>566.65</v>
       </c>
       <c r="F44" t="n">
-        <v>37709</v>
+        <v>26333</v>
       </c>
       <c r="G44" t="n">
-        <v>505</v>
+        <v>352</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>3504.41</v>
+        <v>1839.82</v>
       </c>
       <c r="K44" t="n">
-        <v>4.32</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="45">
@@ -4838,30 +4838,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>项目19</t>
+          <t>项目20</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1068.54</v>
+        <v>746.1900000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>54343</v>
+        <v>37949</v>
       </c>
       <c r="G45" t="n">
-        <v>1702</v>
+        <v>1189</v>
       </c>
       <c r="H45" t="n">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>4968.74</v>
+        <v>3726.56</v>
       </c>
       <c r="K45" t="n">
-        <v>4.65</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="46">
@@ -4875,30 +4875,30 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>项目18</t>
+          <t>项目1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1129.56</v>
+        <v>788.8</v>
       </c>
       <c r="F46" t="n">
-        <v>61010</v>
+        <v>42604</v>
       </c>
       <c r="G46" t="n">
-        <v>632</v>
+        <v>441</v>
       </c>
       <c r="H46" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>5398.08</v>
+        <v>4048.57</v>
       </c>
       <c r="K46" t="n">
-        <v>4.78</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="47">
@@ -4917,25 +4917,25 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>625.2</v>
+        <v>521.9</v>
       </c>
       <c r="F47" t="n">
-        <v>25035</v>
+        <v>20899</v>
       </c>
       <c r="G47" t="n">
-        <v>770</v>
+        <v>642</v>
       </c>
       <c r="H47" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>2733.53</v>
+        <v>2200.42</v>
       </c>
       <c r="K47" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="48">
@@ -4954,25 +4954,25 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>760.01</v>
+        <v>634.4400000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>27468</v>
+        <v>22929</v>
       </c>
       <c r="G48" t="n">
-        <v>744</v>
+        <v>621</v>
       </c>
       <c r="H48" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>6371.86</v>
+        <v>5471.11</v>
       </c>
       <c r="K48" t="n">
-        <v>8.380000000000001</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4991,25 +4991,25 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>803.02</v>
+        <v>670.34</v>
       </c>
       <c r="F49" t="n">
-        <v>38538</v>
+        <v>32170</v>
       </c>
       <c r="G49" t="n">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="H49" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>1316.52</v>
+        <v>1413.02</v>
       </c>
       <c r="K49" t="n">
-        <v>1.64</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="50">
@@ -5028,22 +5028,22 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>764.0700000000001</v>
+        <v>637.83</v>
       </c>
       <c r="F50" t="n">
-        <v>26972</v>
+        <v>22516</v>
       </c>
       <c r="G50" t="n">
-        <v>844</v>
+        <v>704</v>
       </c>
       <c r="H50" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
-        <v>5929.27</v>
+        <v>4949.67</v>
       </c>
       <c r="K50" t="n">
         <v>7.76</v>
@@ -5065,25 +5065,25 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>645.39</v>
+        <v>538.75</v>
       </c>
       <c r="F51" t="n">
-        <v>22774</v>
+        <v>19011</v>
       </c>
       <c r="G51" t="n">
-        <v>774</v>
+        <v>646</v>
       </c>
       <c r="H51" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>6499.45</v>
+        <v>5580.66</v>
       </c>
       <c r="K51" t="n">
-        <v>10.07</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="52">
@@ -5106,25 +5106,25 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>594.13</v>
+        <v>492.92</v>
       </c>
       <c r="F52" t="n">
-        <v>15042</v>
+        <v>12479</v>
       </c>
       <c r="G52" t="n">
-        <v>471</v>
+        <v>391</v>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>2974.38</v>
+        <v>2570.99</v>
       </c>
       <c r="K52" t="n">
-        <v>5.01</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="53">
@@ -5143,25 +5143,25 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>828.13</v>
+        <v>687.0599999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>36857</v>
+        <v>30579</v>
       </c>
       <c r="G53" t="n">
-        <v>409</v>
+        <v>339</v>
       </c>
       <c r="H53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>1759.1</v>
+        <v>1267.11</v>
       </c>
       <c r="K53" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="54">
@@ -5184,25 +5184,25 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>614.41</v>
+        <v>509.74</v>
       </c>
       <c r="F54" t="n">
-        <v>20538</v>
+        <v>17039</v>
       </c>
       <c r="G54" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="H54" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I54" t="n">
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>1234.03</v>
+        <v>1333.33</v>
       </c>
       <c r="K54" t="n">
-        <v>2.01</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="55">
@@ -5221,25 +5221,25 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>739.71</v>
+        <v>613.7</v>
       </c>
       <c r="F55" t="n">
-        <v>19895</v>
+        <v>16506</v>
       </c>
       <c r="G55" t="n">
-        <v>458</v>
+        <v>380</v>
       </c>
       <c r="H55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3796.09</v>
+        <v>3417.97</v>
       </c>
       <c r="K55" t="n">
-        <v>5.13</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="56">
@@ -5262,25 +5262,25 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>799.41</v>
+        <v>663.24</v>
       </c>
       <c r="F56" t="n">
-        <v>32768</v>
+        <v>27186</v>
       </c>
       <c r="G56" t="n">
-        <v>414</v>
+        <v>343</v>
       </c>
       <c r="H56" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>4294.02</v>
+        <v>3313.98</v>
       </c>
       <c r="K56" t="n">
-        <v>5.37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -5303,25 +5303,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1009.6</v>
+        <v>1309.62</v>
       </c>
       <c r="F57" t="n">
-        <v>27919</v>
+        <v>36216</v>
       </c>
       <c r="G57" t="n">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="H57" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>6011.61</v>
+        <v>7935.43</v>
       </c>
       <c r="K57" t="n">
-        <v>5.95</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="58">
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>1207.45</v>
+        <v>1566.26</v>
       </c>
       <c r="F58" t="n">
-        <v>40090</v>
+        <v>52003</v>
       </c>
       <c r="G58" t="n">
-        <v>544</v>
+        <v>706</v>
       </c>
       <c r="H58" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>6515.7</v>
+        <v>8600.83</v>
       </c>
       <c r="K58" t="n">
-        <v>5.4</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="59">
@@ -5377,25 +5377,25 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>1738.41</v>
+        <v>2255</v>
       </c>
       <c r="F59" t="n">
-        <v>47225</v>
+        <v>61258</v>
       </c>
       <c r="G59" t="n">
-        <v>1264</v>
+        <v>1639</v>
       </c>
       <c r="H59" t="n">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>6226.49</v>
+        <v>8219.07</v>
       </c>
       <c r="K59" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="60">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>项目10</t>
+          <t>项目11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5418,25 +5418,25 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1515.41</v>
+        <v>1965.74</v>
       </c>
       <c r="F60" t="n">
-        <v>41977</v>
+        <v>54451</v>
       </c>
       <c r="G60" t="n">
-        <v>709</v>
+        <v>920</v>
       </c>
       <c r="H60" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>6111.08</v>
+        <v>8066.72</v>
       </c>
       <c r="K60" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="61">
@@ -5459,25 +5459,25 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1385.53</v>
+        <v>1797.28</v>
       </c>
       <c r="F61" t="n">
-        <v>45257</v>
+        <v>58706</v>
       </c>
       <c r="G61" t="n">
-        <v>791</v>
+        <v>1026</v>
       </c>
       <c r="H61" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>6264.04</v>
+        <v>8268.629999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="62">
@@ -5500,25 +5500,25 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12616.26</v>
+        <v>11333.57</v>
       </c>
       <c r="F62" t="n">
-        <v>318365</v>
+        <v>285997</v>
       </c>
       <c r="G62" t="n">
-        <v>10533</v>
+        <v>9462</v>
       </c>
       <c r="H62" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>25372.13</v>
+        <v>22035.38</v>
       </c>
       <c r="K62" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="63">
@@ -5541,25 +5541,25 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11160.87</v>
+        <v>10026.15</v>
       </c>
       <c r="F63" t="n">
-        <v>284409</v>
+        <v>255493</v>
       </c>
       <c r="G63" t="n">
-        <v>5984</v>
+        <v>5375</v>
       </c>
       <c r="H63" t="n">
-        <v>715</v>
+        <v>643</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>23948.08</v>
+        <v>20798.62</v>
       </c>
       <c r="K63" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="64">
@@ -5582,25 +5582,25 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11071.95</v>
+        <v>9946.27</v>
       </c>
       <c r="F64" t="n">
-        <v>311233</v>
+        <v>279590</v>
       </c>
       <c r="G64" t="n">
-        <v>9397</v>
+        <v>8441</v>
       </c>
       <c r="H64" t="n">
-        <v>1630</v>
+        <v>1464</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>24794.79</v>
+        <v>21533.97</v>
       </c>
       <c r="K64" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="65">
@@ -5623,25 +5623,25 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13861.61</v>
+        <v>12452.31</v>
       </c>
       <c r="F65" t="n">
-        <v>656944</v>
+        <v>590153</v>
       </c>
       <c r="G65" t="n">
-        <v>19817</v>
+        <v>17802</v>
       </c>
       <c r="H65" t="n">
-        <v>1545</v>
+        <v>1388</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>25372.95</v>
+        <v>22036.09</v>
       </c>
       <c r="K65" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="66">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>项目8</t>
+          <t>项目9</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5664,25 +5664,25 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8508.09</v>
+        <v>7643.06</v>
       </c>
       <c r="F66" t="n">
-        <v>383127</v>
+        <v>344174</v>
       </c>
       <c r="G66" t="n">
-        <v>3499</v>
+        <v>3143</v>
       </c>
       <c r="H66" t="n">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>25450.13</v>
+        <v>22103.12</v>
       </c>
       <c r="K66" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="67">
@@ -5705,25 +5705,25 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10268.5</v>
+        <v>11602.15</v>
       </c>
       <c r="F67" t="n">
-        <v>532594</v>
+        <v>601766</v>
       </c>
       <c r="G67" t="n">
-        <v>15588</v>
+        <v>17612</v>
       </c>
       <c r="H67" t="n">
-        <v>1991</v>
+        <v>2249</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>26313.61</v>
+        <v>29864.67</v>
       </c>
       <c r="K67" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="68">
@@ -5742,25 +5742,25 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>8490.629999999999</v>
+        <v>9593.379999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>276902</v>
+        <v>312866</v>
       </c>
       <c r="G68" t="n">
-        <v>9264</v>
+        <v>10467</v>
       </c>
       <c r="H68" t="n">
-        <v>1521</v>
+        <v>1719</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>26501.18</v>
+        <v>30077.55</v>
       </c>
       <c r="K68" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="69">
@@ -5783,25 +5783,25 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7288.36</v>
+        <v>8234.950000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>270703</v>
+        <v>305861</v>
       </c>
       <c r="G69" t="n">
-        <v>5038</v>
+        <v>5693</v>
       </c>
       <c r="H69" t="n">
-        <v>543</v>
+        <v>614</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>26936.43</v>
+        <v>30571.53</v>
       </c>
       <c r="K69" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="70">
@@ -5824,25 +5824,25 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7031.16</v>
+        <v>7944.35</v>
       </c>
       <c r="F70" t="n">
-        <v>397696</v>
+        <v>449348</v>
       </c>
       <c r="G70" t="n">
-        <v>11354</v>
+        <v>12829</v>
       </c>
       <c r="H70" t="n">
-        <v>945</v>
+        <v>1068</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>25750.4</v>
+        <v>29225.45</v>
       </c>
       <c r="K70" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="71">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>项目15</t>
+          <t>项目16</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5865,25 +5865,25 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8267.25</v>
+        <v>9340.98</v>
       </c>
       <c r="F71" t="n">
-        <v>221425</v>
+        <v>250183</v>
       </c>
       <c r="G71" t="n">
-        <v>2752</v>
+        <v>3110</v>
       </c>
       <c r="H71" t="n">
-        <v>478</v>
+        <v>541</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>26372.41</v>
+        <v>29931.4</v>
       </c>
       <c r="K71" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="72">
@@ -5906,25 +5906,25 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10312.53</v>
+        <v>12293.91</v>
       </c>
       <c r="F72" t="n">
-        <v>267646</v>
+        <v>319070</v>
       </c>
       <c r="G72" t="n">
-        <v>8951</v>
+        <v>10670</v>
       </c>
       <c r="H72" t="n">
-        <v>1601</v>
+        <v>1909</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J72" t="n">
-        <v>26340.65</v>
+        <v>31443.54</v>
       </c>
       <c r="K72" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="73">
@@ -5947,22 +5947,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>13484.36</v>
+        <v>16075.14</v>
       </c>
       <c r="F73" t="n">
-        <v>393973</v>
+        <v>469668</v>
       </c>
       <c r="G73" t="n">
-        <v>6700</v>
+        <v>7988</v>
       </c>
       <c r="H73" t="n">
-        <v>515</v>
+        <v>614</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J73" t="n">
-        <v>25570.42</v>
+        <v>30524.08</v>
       </c>
       <c r="K73" t="n">
         <v>1.9</v>
@@ -5988,22 +5988,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>13994.85</v>
+        <v>16683.71</v>
       </c>
       <c r="F74" t="n">
-        <v>713423</v>
+        <v>850494</v>
       </c>
       <c r="G74" t="n">
-        <v>21713</v>
+        <v>25884</v>
       </c>
       <c r="H74" t="n">
-        <v>2949</v>
+        <v>3516</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J74" t="n">
-        <v>26336.54</v>
+        <v>31438.63</v>
       </c>
       <c r="K74" t="n">
         <v>1.88</v>
@@ -6029,22 +6029,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>8555.620000000001</v>
+        <v>10199.43</v>
       </c>
       <c r="F75" t="n">
-        <v>269912</v>
+        <v>321771</v>
       </c>
       <c r="G75" t="n">
-        <v>7725</v>
+        <v>9209</v>
       </c>
       <c r="H75" t="n">
-        <v>811</v>
+        <v>966</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>26490.13</v>
+        <v>31621.97</v>
       </c>
       <c r="K75" t="n">
         <v>3.1</v>
@@ -6070,22 +6070,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11048.2</v>
+        <v>13170.93</v>
       </c>
       <c r="F76" t="n">
-        <v>564509</v>
+        <v>672970</v>
       </c>
       <c r="G76" t="n">
-        <v>8011</v>
+        <v>9550</v>
       </c>
       <c r="H76" t="n">
-        <v>910</v>
+        <v>1085</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J76" t="n">
-        <v>26744.96</v>
+        <v>31926.17</v>
       </c>
       <c r="K76" t="n">
         <v>2.42</v>
@@ -6111,25 +6111,25 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>14084.08</v>
+        <v>15244.11</v>
       </c>
       <c r="F77" t="n">
-        <v>546422</v>
+        <v>591427</v>
       </c>
       <c r="G77" t="n">
-        <v>18541</v>
+        <v>20069</v>
       </c>
       <c r="H77" t="n">
-        <v>3001</v>
+        <v>3249</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>24174.96</v>
+        <v>26618.02</v>
       </c>
       <c r="K77" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="78">
@@ -6152,25 +6152,25 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>13330.61</v>
+        <v>14428.59</v>
       </c>
       <c r="F78" t="n">
-        <v>731378</v>
+        <v>791619</v>
       </c>
       <c r="G78" t="n">
-        <v>16342</v>
+        <v>17688</v>
       </c>
       <c r="H78" t="n">
-        <v>2172</v>
+        <v>2351</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>24738.05</v>
+        <v>27238.02</v>
       </c>
       <c r="K78" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="79">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18118.83</v>
+        <v>19611.18</v>
       </c>
       <c r="F79" t="n">
-        <v>680112</v>
+        <v>736129</v>
       </c>
       <c r="G79" t="n">
-        <v>5502</v>
+        <v>5955</v>
       </c>
       <c r="H79" t="n">
-        <v>753</v>
+        <v>815</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>25440.48</v>
+        <v>28011.43</v>
       </c>
       <c r="K79" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="80">
@@ -6234,25 +6234,25 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>21128.28</v>
+        <v>22868.51</v>
       </c>
       <c r="F80" t="n">
-        <v>703946</v>
+        <v>761927</v>
       </c>
       <c r="G80" t="n">
-        <v>8313</v>
+        <v>8998</v>
       </c>
       <c r="H80" t="n">
-        <v>938</v>
+        <v>1015</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>25471.26</v>
+        <v>28045.32</v>
       </c>
       <c r="K80" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="81">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>项目4</t>
+          <t>项目5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>13418.04</v>
+        <v>14523.23</v>
       </c>
       <c r="F81" t="n">
-        <v>361823</v>
+        <v>391625</v>
       </c>
       <c r="G81" t="n">
-        <v>4356</v>
+        <v>4715</v>
       </c>
       <c r="H81" t="n">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>24956.09</v>
+        <v>27478.09</v>
       </c>
       <c r="K81" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="82">
@@ -6312,25 +6312,25 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12084.48</v>
+        <v>10025.64</v>
       </c>
       <c r="F82" t="n">
-        <v>345336</v>
+        <v>286501</v>
       </c>
       <c r="G82" t="n">
-        <v>4326</v>
+        <v>3589</v>
       </c>
       <c r="H82" t="n">
-        <v>564</v>
+        <v>467</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>30914.79</v>
+        <v>25525.88</v>
       </c>
       <c r="K82" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="83">
@@ -6349,25 +6349,25 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>14301.5</v>
+        <v>11864.95</v>
       </c>
       <c r="F83" t="n">
-        <v>478354</v>
+        <v>396857</v>
       </c>
       <c r="G83" t="n">
-        <v>4646</v>
+        <v>3855</v>
       </c>
       <c r="H83" t="n">
-        <v>338</v>
+        <v>280</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>28774.23</v>
+        <v>23758.45</v>
       </c>
       <c r="K83" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -6386,25 +6386,25 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>14581.27</v>
+        <v>12097.06</v>
       </c>
       <c r="F84" t="n">
-        <v>396096</v>
+        <v>328613</v>
       </c>
       <c r="G84" t="n">
-        <v>7748</v>
+        <v>6428</v>
       </c>
       <c r="H84" t="n">
-        <v>716</v>
+        <v>594</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>30867.27</v>
+        <v>25486.64</v>
       </c>
       <c r="K84" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="85">
@@ -6427,25 +6427,25 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>14980.69</v>
+        <v>12428.43</v>
       </c>
       <c r="F85" t="n">
-        <v>424415</v>
+        <v>352107</v>
       </c>
       <c r="G85" t="n">
-        <v>10901</v>
+        <v>9044</v>
       </c>
       <c r="H85" t="n">
-        <v>1165</v>
+        <v>967</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>28559.98</v>
+        <v>23581.55</v>
       </c>
       <c r="K85" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="86">
@@ -6468,25 +6468,25 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10954.66</v>
+        <v>9088.32</v>
       </c>
       <c r="F86" t="n">
-        <v>400249</v>
+        <v>332059</v>
       </c>
       <c r="G86" t="n">
-        <v>8845</v>
+        <v>7338</v>
       </c>
       <c r="H86" t="n">
-        <v>1038</v>
+        <v>861</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>29235.89</v>
+        <v>24139.63</v>
       </c>
       <c r="K86" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="87">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>12198.45</v>
+        <v>10752.07</v>
       </c>
       <c r="F87" t="n">
-        <v>381455</v>
+        <v>336226</v>
       </c>
       <c r="G87" t="n">
-        <v>11081</v>
+        <v>9767</v>
       </c>
       <c r="H87" t="n">
-        <v>815</v>
+        <v>718</v>
       </c>
       <c r="I87" t="n">
         <v>15</v>
       </c>
       <c r="J87" t="n">
-        <v>14367.05</v>
+        <v>13118.41</v>
       </c>
       <c r="K87" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="88">
@@ -6550,25 +6550,25 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>12549.25</v>
+        <v>11061.29</v>
       </c>
       <c r="F88" t="n">
-        <v>381457</v>
+        <v>336228</v>
       </c>
       <c r="G88" t="n">
-        <v>4236</v>
+        <v>3734</v>
       </c>
       <c r="H88" t="n">
-        <v>524</v>
+        <v>462</v>
       </c>
       <c r="I88" t="n">
         <v>15</v>
       </c>
       <c r="J88" t="n">
-        <v>15654.62</v>
+        <v>14294.08</v>
       </c>
       <c r="K88" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="89">
@@ -6591,25 +6591,25 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>15546.67</v>
+        <v>13703.3</v>
       </c>
       <c r="F89" t="n">
-        <v>793531</v>
+        <v>699442</v>
       </c>
       <c r="G89" t="n">
-        <v>21360</v>
+        <v>18827</v>
       </c>
       <c r="H89" t="n">
-        <v>1357</v>
+        <v>1196</v>
       </c>
       <c r="I89" t="n">
         <v>15</v>
       </c>
       <c r="J89" t="n">
-        <v>14590.69</v>
+        <v>13322.61</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="90">
@@ -6632,25 +6632,25 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>11160.26</v>
+        <v>9836.99</v>
       </c>
       <c r="F90" t="n">
-        <v>303034</v>
+        <v>267103</v>
       </c>
       <c r="G90" t="n">
-        <v>3054</v>
+        <v>2692</v>
       </c>
       <c r="H90" t="n">
-        <v>481</v>
+        <v>424</v>
       </c>
       <c r="I90" t="n">
         <v>15</v>
       </c>
       <c r="J90" t="n">
-        <v>15570.9</v>
+        <v>14217.63</v>
       </c>
       <c r="K90" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="91">
@@ -6669,25 +6669,25 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>17699.5</v>
+        <v>15600.87</v>
       </c>
       <c r="F91" t="n">
-        <v>592151</v>
+        <v>521940</v>
       </c>
       <c r="G91" t="n">
-        <v>6535</v>
+        <v>5760</v>
       </c>
       <c r="H91" t="n">
-        <v>984</v>
+        <v>867</v>
       </c>
       <c r="I91" t="n">
         <v>15</v>
       </c>
       <c r="J91" t="n">
-        <v>14624.38</v>
+        <v>13353.37</v>
       </c>
       <c r="K91" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="92">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>3472.1</v>
+        <v>3112.88</v>
       </c>
       <c r="F92" t="n">
-        <v>228978</v>
+        <v>205288</v>
       </c>
       <c r="G92" t="n">
-        <v>2438</v>
+        <v>2185</v>
       </c>
       <c r="H92" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="I92" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
-        <v>16194.64</v>
+        <v>14905.19</v>
       </c>
       <c r="K92" t="n">
-        <v>4.66</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="93">
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>4305.67</v>
+        <v>3860.21</v>
       </c>
       <c r="F93" t="n">
-        <v>145852</v>
+        <v>130762</v>
       </c>
       <c r="G93" t="n">
-        <v>1609</v>
+        <v>1442</v>
       </c>
       <c r="H93" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="I93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J93" t="n">
-        <v>15340.85</v>
+        <v>14119.38</v>
       </c>
       <c r="K93" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="94">
@@ -6780,25 +6780,25 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>2614.31</v>
+        <v>2343.83</v>
       </c>
       <c r="F94" t="n">
-        <v>90331</v>
+        <v>80985</v>
       </c>
       <c r="G94" t="n">
-        <v>1709</v>
+        <v>1532</v>
       </c>
       <c r="H94" t="n">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="I94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J94" t="n">
-        <v>15332.14</v>
+        <v>14111.36</v>
       </c>
       <c r="K94" t="n">
-        <v>5.86</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="95">
@@ -6817,25 +6817,25 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>4107.85</v>
+        <v>3682.85</v>
       </c>
       <c r="F95" t="n">
-        <v>110357</v>
+        <v>98939</v>
       </c>
       <c r="G95" t="n">
-        <v>3834</v>
+        <v>3437</v>
       </c>
       <c r="H95" t="n">
-        <v>543</v>
+        <v>487</v>
       </c>
       <c r="I95" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J95" t="n">
-        <v>15224.71</v>
+        <v>14012.49</v>
       </c>
       <c r="K95" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="96">
@@ -6849,30 +6849,30 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>项目20</t>
+          <t>项目1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>4655.32</v>
+        <v>4173.67</v>
       </c>
       <c r="F96" t="n">
-        <v>193439</v>
+        <v>173425</v>
       </c>
       <c r="G96" t="n">
-        <v>3195</v>
+        <v>2864</v>
       </c>
       <c r="H96" t="n">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="I96" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J96" t="n">
-        <v>16186.84</v>
+        <v>14898.01</v>
       </c>
       <c r="K96" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="97">
@@ -6891,25 +6891,25 @@
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>3859.95</v>
+        <v>6389.57</v>
       </c>
       <c r="F97" t="n">
-        <v>207013</v>
+        <v>342679</v>
       </c>
       <c r="G97" t="n">
-        <v>5941</v>
+        <v>9834</v>
       </c>
       <c r="H97" t="n">
-        <v>1028</v>
+        <v>1702</v>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J97" t="n">
-        <v>10132.14</v>
+        <v>17452.17</v>
       </c>
       <c r="K97" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="98">
@@ -6928,25 +6928,25 @@
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>4335.26</v>
+        <v>7176.37</v>
       </c>
       <c r="F98" t="n">
-        <v>229485</v>
+        <v>379878</v>
       </c>
       <c r="G98" t="n">
-        <v>3524</v>
+        <v>5834</v>
       </c>
       <c r="H98" t="n">
-        <v>549</v>
+        <v>909</v>
       </c>
       <c r="I98" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J98" t="n">
-        <v>10529.97</v>
+        <v>18137.4</v>
       </c>
       <c r="K98" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="99">
@@ -6969,25 +6969,25 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4128.71</v>
+        <v>6834.46</v>
       </c>
       <c r="F99" t="n">
-        <v>145660</v>
+        <v>241119</v>
       </c>
       <c r="G99" t="n">
-        <v>5071</v>
+        <v>8395</v>
       </c>
       <c r="H99" t="n">
-        <v>504</v>
+        <v>835</v>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J99" t="n">
-        <v>10202.68</v>
+        <v>17573.67</v>
       </c>
       <c r="K99" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="100">
@@ -7010,25 +7010,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4424.58</v>
+        <v>7324.23</v>
       </c>
       <c r="F100" t="n">
-        <v>168080</v>
+        <v>278232</v>
       </c>
       <c r="G100" t="n">
-        <v>2312</v>
+        <v>3828</v>
       </c>
       <c r="H100" t="n">
-        <v>306</v>
+        <v>508</v>
       </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J100" t="n">
-        <v>10174.87</v>
+        <v>17525.77</v>
       </c>
       <c r="K100" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="101">
@@ -7051,25 +7051,25 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5811.62</v>
+        <v>9620.280000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>146359</v>
+        <v>242277</v>
       </c>
       <c r="G101" t="n">
-        <v>2631</v>
+        <v>4355</v>
       </c>
       <c r="H101" t="n">
-        <v>407</v>
+        <v>675</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J101" t="n">
-        <v>10447.38</v>
+        <v>17995.15</v>
       </c>
       <c r="K101" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="102">
@@ -7092,22 +7092,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4526.93</v>
+        <v>4571.19</v>
       </c>
       <c r="F102" t="n">
-        <v>115152</v>
+        <v>116278</v>
       </c>
       <c r="G102" t="n">
-        <v>2442</v>
+        <v>2466</v>
       </c>
       <c r="H102" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I102" t="n">
         <v>12</v>
       </c>
       <c r="J102" t="n">
-        <v>17348.67</v>
+        <v>17518.25</v>
       </c>
       <c r="K102" t="n">
         <v>3.83</v>
@@ -7129,22 +7129,22 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>5000.17</v>
+        <v>5049.06</v>
       </c>
       <c r="F103" t="n">
-        <v>160424</v>
+        <v>161992</v>
       </c>
       <c r="G103" t="n">
-        <v>2109</v>
+        <v>2130</v>
       </c>
       <c r="H103" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I103" t="n">
         <v>12</v>
       </c>
       <c r="J103" t="n">
-        <v>18205.06</v>
+        <v>18383.01</v>
       </c>
       <c r="K103" t="n">
         <v>3.64</v>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>项目17</t>
+          <t>项目18</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7170,22 +7170,22 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4579.89</v>
+        <v>4624.67</v>
       </c>
       <c r="F104" t="n">
-        <v>185346</v>
+        <v>187159</v>
       </c>
       <c r="G104" t="n">
-        <v>1786</v>
+        <v>1804</v>
       </c>
       <c r="H104" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I104" t="n">
         <v>12</v>
       </c>
       <c r="J104" t="n">
-        <v>18236.49</v>
+        <v>18414.75</v>
       </c>
       <c r="K104" t="n">
         <v>3.98</v>
@@ -7211,22 +7211,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4099.6</v>
+        <v>4139.68</v>
       </c>
       <c r="F105" t="n">
-        <v>139181</v>
+        <v>140542</v>
       </c>
       <c r="G105" t="n">
-        <v>3670</v>
+        <v>3706</v>
       </c>
       <c r="H105" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I105" t="n">
         <v>12</v>
       </c>
       <c r="J105" t="n">
-        <v>17108</v>
+        <v>17275.22</v>
       </c>
       <c r="K105" t="n">
         <v>4.17</v>
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4586.78</v>
+        <v>4631.62</v>
       </c>
       <c r="F106" t="n">
-        <v>256356</v>
+        <v>258863</v>
       </c>
       <c r="G106" t="n">
-        <v>8836</v>
+        <v>8922</v>
       </c>
       <c r="H106" t="n">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="I106" t="n">
         <v>12</v>
       </c>
       <c r="J106" t="n">
-        <v>17515.15</v>
+        <v>17686.36</v>
       </c>
       <c r="K106" t="n">
         <v>3.82</v>
@@ -7289,25 +7289,25 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>7010.91</v>
+        <v>5110.91</v>
       </c>
       <c r="F107" t="n">
-        <v>233880</v>
+        <v>170497</v>
       </c>
       <c r="G107" t="n">
-        <v>5717</v>
+        <v>4168</v>
       </c>
       <c r="H107" t="n">
-        <v>886</v>
+        <v>646</v>
       </c>
       <c r="I107" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J107" t="n">
-        <v>18767.39</v>
+        <v>13134.07</v>
       </c>
       <c r="K107" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="108">
@@ -7326,25 +7326,25 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>6471.75</v>
+        <v>4717.87</v>
       </c>
       <c r="F108" t="n">
-        <v>341021</v>
+        <v>248603</v>
       </c>
       <c r="G108" t="n">
-        <v>7882</v>
+        <v>5746</v>
       </c>
       <c r="H108" t="n">
-        <v>1319</v>
+        <v>961</v>
       </c>
       <c r="I108" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J108" t="n">
-        <v>19005.1</v>
+        <v>13300.42</v>
       </c>
       <c r="K108" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="109">
@@ -7363,25 +7363,25 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>4811.83</v>
+        <v>3507.79</v>
       </c>
       <c r="F109" t="n">
-        <v>140258</v>
+        <v>102247</v>
       </c>
       <c r="G109" t="n">
-        <v>1889</v>
+        <v>1377</v>
       </c>
       <c r="H109" t="n">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="I109" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J109" t="n">
-        <v>19486.47</v>
+        <v>13637.31</v>
       </c>
       <c r="K109" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="110">
@@ -7395,30 +7395,30 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>项目6</t>
+          <t>项目7</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>6396.84</v>
+        <v>4663.25</v>
       </c>
       <c r="F110" t="n">
-        <v>403861</v>
+        <v>294412</v>
       </c>
       <c r="G110" t="n">
-        <v>12189</v>
+        <v>8885</v>
       </c>
       <c r="H110" t="n">
-        <v>746</v>
+        <v>544</v>
       </c>
       <c r="I110" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J110" t="n">
-        <v>18496.22</v>
+        <v>12944.29</v>
       </c>
       <c r="K110" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="111">
@@ -7432,30 +7432,30 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>项目13</t>
+          <t>项目14</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>4312.77</v>
+        <v>3143.99</v>
       </c>
       <c r="F111" t="n">
-        <v>215112</v>
+        <v>156815</v>
       </c>
       <c r="G111" t="n">
-        <v>4952</v>
+        <v>3610</v>
       </c>
       <c r="H111" t="n">
-        <v>536</v>
+        <v>390</v>
       </c>
       <c r="I111" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J111" t="n">
-        <v>19396.83</v>
+        <v>13574.57</v>
       </c>
       <c r="K111" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="112">
@@ -7474,25 +7474,25 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>3818.38</v>
+        <v>3491.39</v>
       </c>
       <c r="F112" t="n">
-        <v>111986</v>
+        <v>102396</v>
       </c>
       <c r="G112" t="n">
-        <v>3171</v>
+        <v>2899</v>
       </c>
       <c r="H112" t="n">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="I112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J112" t="n">
-        <v>12503.52</v>
+        <v>11219.4</v>
       </c>
       <c r="K112" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="113">
@@ -7515,25 +7515,25 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4428.62</v>
+        <v>4049.37</v>
       </c>
       <c r="F113" t="n">
-        <v>175961</v>
+        <v>160892</v>
       </c>
       <c r="G113" t="n">
-        <v>5440</v>
+        <v>4974</v>
       </c>
       <c r="H113" t="n">
-        <v>686</v>
+        <v>627</v>
       </c>
       <c r="I113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J113" t="n">
-        <v>12569.94</v>
+        <v>11279</v>
       </c>
       <c r="K113" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="114">
@@ -7552,25 +7552,25 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>5000.83</v>
+        <v>4572.58</v>
       </c>
       <c r="F114" t="n">
-        <v>159821</v>
+        <v>146135</v>
       </c>
       <c r="G114" t="n">
-        <v>1778</v>
+        <v>1625</v>
       </c>
       <c r="H114" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="I114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J114" t="n">
-        <v>13744.96</v>
+        <v>12333.34</v>
       </c>
       <c r="K114" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="115">
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>3199.93</v>
+        <v>2925.9</v>
       </c>
       <c r="F115" t="n">
-        <v>159692</v>
+        <v>146016</v>
       </c>
       <c r="G115" t="n">
-        <v>3707</v>
+        <v>3390</v>
       </c>
       <c r="H115" t="n">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="I115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J115" t="n">
-        <v>12551</v>
+        <v>11262.01</v>
       </c>
       <c r="K115" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="116">
@@ -7630,25 +7630,25 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4854.35</v>
+        <v>4438.65</v>
       </c>
       <c r="F116" t="n">
-        <v>158696</v>
+        <v>145106</v>
       </c>
       <c r="G116" t="n">
-        <v>3382</v>
+        <v>3092</v>
       </c>
       <c r="H116" t="n">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="I116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J116" t="n">
-        <v>12733.41</v>
+        <v>11425.68</v>
       </c>
       <c r="K116" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="117">
@@ -7667,25 +7667,25 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>3652.28</v>
+        <v>3029.16</v>
       </c>
       <c r="F117" t="n">
-        <v>162894</v>
+        <v>135103</v>
       </c>
       <c r="G117" t="n">
-        <v>2924</v>
+        <v>2425</v>
       </c>
       <c r="H117" t="n">
-        <v>348</v>
+        <v>289</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>9324.860000000001</v>
+        <v>7158.9</v>
       </c>
       <c r="K117" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="118">
@@ -7704,25 +7704,25 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>4237.81</v>
+        <v>3514.79</v>
       </c>
       <c r="F118" t="n">
-        <v>107231</v>
+        <v>88936</v>
       </c>
       <c r="G118" t="n">
-        <v>2390</v>
+        <v>1982</v>
       </c>
       <c r="H118" t="n">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
-        <v>9235.41</v>
+        <v>7090.24</v>
       </c>
       <c r="K118" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="119">
@@ -7741,25 +7741,25 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>3399.71</v>
+        <v>2819.68</v>
       </c>
       <c r="F119" t="n">
-        <v>97113</v>
+        <v>80545</v>
       </c>
       <c r="G119" t="n">
-        <v>3162</v>
+        <v>2623</v>
       </c>
       <c r="H119" t="n">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="I119" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J119" t="n">
-        <v>8500.93</v>
+        <v>6526.35</v>
       </c>
       <c r="K119" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="120">
@@ -7773,30 +7773,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>项目17</t>
+          <t>项目18</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>3833.81</v>
+        <v>3179.71</v>
       </c>
       <c r="F120" t="n">
-        <v>171724</v>
+        <v>142426</v>
       </c>
       <c r="G120" t="n">
-        <v>3956</v>
+        <v>3281</v>
       </c>
       <c r="H120" t="n">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J120" t="n">
-        <v>8683.9</v>
+        <v>6666.83</v>
       </c>
       <c r="K120" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="121">
@@ -7815,25 +7815,25 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>4293.49</v>
+        <v>3560.96</v>
       </c>
       <c r="F121" t="n">
-        <v>204961</v>
+        <v>169991</v>
       </c>
       <c r="G121" t="n">
-        <v>4481</v>
+        <v>3717</v>
       </c>
       <c r="H121" t="n">
-        <v>367</v>
+        <v>304</v>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>9098.370000000001</v>
+        <v>6985.02</v>
       </c>
       <c r="K121" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="122">
@@ -7856,25 +7856,25 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>8080.57</v>
+        <v>6823.34</v>
       </c>
       <c r="F122" t="n">
-        <v>222017</v>
+        <v>187474</v>
       </c>
       <c r="G122" t="n">
-        <v>5075</v>
+        <v>4285</v>
       </c>
       <c r="H122" t="n">
-        <v>700</v>
+        <v>591</v>
       </c>
       <c r="I122" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J122" t="n">
-        <v>16793.11</v>
+        <v>13997.12</v>
       </c>
       <c r="K122" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="123">
@@ -7897,25 +7897,25 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5895.73</v>
+        <v>4978.43</v>
       </c>
       <c r="F123" t="n">
-        <v>339183</v>
+        <v>286410</v>
       </c>
       <c r="G123" t="n">
-        <v>3724</v>
+        <v>3145</v>
       </c>
       <c r="H123" t="n">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="I123" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J123" t="n">
-        <v>16531.4</v>
+        <v>13778.99</v>
       </c>
       <c r="K123" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="124">
@@ -7938,25 +7938,25 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>7355.99</v>
+        <v>6211.5</v>
       </c>
       <c r="F124" t="n">
-        <v>286754</v>
+        <v>242139</v>
       </c>
       <c r="G124" t="n">
-        <v>2458</v>
+        <v>2075</v>
       </c>
       <c r="H124" t="n">
-        <v>365</v>
+        <v>308</v>
       </c>
       <c r="I124" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J124" t="n">
-        <v>16181.79</v>
+        <v>13487.59</v>
       </c>
       <c r="K124" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="125">
@@ -7979,25 +7979,25 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>8818.809999999999</v>
+        <v>7446.72</v>
       </c>
       <c r="F125" t="n">
-        <v>289660</v>
+        <v>244593</v>
       </c>
       <c r="G125" t="n">
-        <v>5970</v>
+        <v>5041</v>
       </c>
       <c r="H125" t="n">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="I125" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J125" t="n">
-        <v>17079.81</v>
+        <v>14236.09</v>
       </c>
       <c r="K125" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="126">
@@ -8011,30 +8011,30 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>项目16</t>
+          <t>项目17</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>9152.280000000001</v>
+        <v>7728.31</v>
       </c>
       <c r="F126" t="n">
-        <v>236253</v>
+        <v>199495</v>
       </c>
       <c r="G126" t="n">
-        <v>5549</v>
+        <v>4686</v>
       </c>
       <c r="H126" t="n">
-        <v>699</v>
+        <v>590</v>
       </c>
       <c r="I126" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J126" t="n">
-        <v>16700.19</v>
+        <v>13919.68</v>
       </c>
       <c r="K126" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="127">
@@ -8057,25 +8057,25 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5103.54</v>
+        <v>7235.22</v>
       </c>
       <c r="F127" t="n">
-        <v>316247</v>
+        <v>448339</v>
       </c>
       <c r="G127" t="n">
-        <v>8253</v>
+        <v>11701</v>
       </c>
       <c r="H127" t="n">
-        <v>602</v>
+        <v>854</v>
       </c>
       <c r="I127" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J127" t="n">
-        <v>18941.41</v>
+        <v>26914.16</v>
       </c>
       <c r="K127" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="128">
@@ -8098,22 +8098,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6688.87</v>
+        <v>9482.73</v>
       </c>
       <c r="F128" t="n">
-        <v>181739</v>
+        <v>257649</v>
       </c>
       <c r="G128" t="n">
-        <v>3957</v>
+        <v>5610</v>
       </c>
       <c r="H128" t="n">
-        <v>276</v>
+        <v>391</v>
       </c>
       <c r="I128" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J128" t="n">
-        <v>17850.81</v>
+        <v>25364.52</v>
       </c>
       <c r="K128" t="n">
         <v>2.67</v>
@@ -8139,25 +8139,25 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4002.29</v>
+        <v>5674</v>
       </c>
       <c r="F129" t="n">
-        <v>113881</v>
+        <v>161448</v>
       </c>
       <c r="G129" t="n">
-        <v>3860</v>
+        <v>5473</v>
       </c>
       <c r="H129" t="n">
-        <v>494</v>
+        <v>701</v>
       </c>
       <c r="I129" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J129" t="n">
-        <v>18296.04</v>
+        <v>25997.14</v>
       </c>
       <c r="K129" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="130">
@@ -8180,25 +8180,25 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5743.73</v>
+        <v>8142.82</v>
       </c>
       <c r="F130" t="n">
-        <v>177202</v>
+        <v>251218</v>
       </c>
       <c r="G130" t="n">
-        <v>1597</v>
+        <v>2264</v>
       </c>
       <c r="H130" t="n">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="I130" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J130" t="n">
-        <v>16024.1</v>
+        <v>26563.73</v>
       </c>
       <c r="K130" t="n">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="131">
@@ -8221,25 +8221,25 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6894.05</v>
+        <v>9773.59</v>
       </c>
       <c r="F131" t="n">
-        <v>262542</v>
+        <v>372202</v>
       </c>
       <c r="G131" t="n">
-        <v>8878</v>
+        <v>12587</v>
       </c>
       <c r="H131" t="n">
-        <v>760</v>
+        <v>1078</v>
       </c>
       <c r="I131" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J131" t="n">
-        <v>18198.77</v>
+        <v>25858.93</v>
       </c>
       <c r="K131" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="132">
@@ -8262,25 +8262,25 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6793.57</v>
+        <v>7051.76</v>
       </c>
       <c r="F132" t="n">
-        <v>218534</v>
+        <v>226839</v>
       </c>
       <c r="G132" t="n">
-        <v>3036</v>
+        <v>3152</v>
       </c>
       <c r="H132" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I132" t="n">
         <v>20</v>
       </c>
       <c r="J132" t="n">
-        <v>13435.09</v>
+        <v>13637.95</v>
       </c>
       <c r="K132" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="133">
@@ -8303,25 +8303,25 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10680.64</v>
+        <v>11086.56</v>
       </c>
       <c r="F133" t="n">
-        <v>293375</v>
+        <v>304524</v>
       </c>
       <c r="G133" t="n">
-        <v>8890</v>
+        <v>9228</v>
       </c>
       <c r="H133" t="n">
-        <v>1051</v>
+        <v>1091</v>
       </c>
       <c r="I133" t="n">
         <v>20</v>
       </c>
       <c r="J133" t="n">
-        <v>13566.41</v>
+        <v>13771.26</v>
       </c>
       <c r="K133" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="134">
@@ -8344,25 +8344,25 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>8163.95</v>
+        <v>8474.219999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>429500</v>
+        <v>445823</v>
       </c>
       <c r="G134" t="n">
-        <v>6689</v>
+        <v>6943</v>
       </c>
       <c r="H134" t="n">
-        <v>669</v>
+        <v>695</v>
       </c>
       <c r="I134" t="n">
         <v>20</v>
       </c>
       <c r="J134" t="n">
-        <v>13035.02</v>
+        <v>13231.84</v>
       </c>
       <c r="K134" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="135">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
-        <v>9093.379999999999</v>
+        <v>9438.969999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>264829</v>
+        <v>274894</v>
       </c>
       <c r="G135" t="n">
-        <v>7176</v>
+        <v>7449</v>
       </c>
       <c r="H135" t="n">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="I135" t="n">
         <v>20</v>
       </c>
       <c r="J135" t="n">
-        <v>13002.41</v>
+        <v>13198.74</v>
       </c>
       <c r="K135" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="136">
@@ -8418,25 +8418,25 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>10497.58</v>
+        <v>10896.56</v>
       </c>
       <c r="F136" t="n">
-        <v>287963</v>
+        <v>298908</v>
       </c>
       <c r="G136" t="n">
-        <v>6058</v>
+        <v>6288</v>
       </c>
       <c r="H136" t="n">
-        <v>754</v>
+        <v>783</v>
       </c>
       <c r="I136" t="n">
         <v>20</v>
       </c>
       <c r="J136" t="n">
-        <v>13764.88</v>
+        <v>13972.72</v>
       </c>
       <c r="K136" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="137">
@@ -8459,25 +8459,25 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9878.629999999999</v>
+        <v>9508.059999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>266241</v>
+        <v>256254</v>
       </c>
       <c r="G137" t="n">
-        <v>6339</v>
+        <v>6101</v>
       </c>
       <c r="H137" t="n">
-        <v>803</v>
+        <v>773</v>
       </c>
       <c r="I137" t="n">
         <v>23</v>
       </c>
       <c r="J137" t="n">
-        <v>15392.07</v>
+        <v>14937.51</v>
       </c>
       <c r="K137" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="138">
@@ -8500,25 +8500,25 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>10897.09</v>
+        <v>10488.32</v>
       </c>
       <c r="F138" t="n">
-        <v>376227</v>
+        <v>362114</v>
       </c>
       <c r="G138" t="n">
-        <v>4030</v>
+        <v>3879</v>
       </c>
       <c r="H138" t="n">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="I138" t="n">
         <v>23</v>
       </c>
       <c r="J138" t="n">
-        <v>16231.36</v>
+        <v>15752.02</v>
       </c>
       <c r="K138" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="139">
@@ -8541,25 +8541,25 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12128.86</v>
+        <v>11673.88</v>
       </c>
       <c r="F139" t="n">
-        <v>473770</v>
+        <v>455998</v>
       </c>
       <c r="G139" t="n">
-        <v>4039</v>
+        <v>3887</v>
       </c>
       <c r="H139" t="n">
-        <v>651</v>
+        <v>626</v>
       </c>
       <c r="I139" t="n">
         <v>23</v>
       </c>
       <c r="J139" t="n">
-        <v>15905.5</v>
+        <v>15435.78</v>
       </c>
       <c r="K139" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="140">
@@ -8582,25 +8582,25 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>9094.959999999999</v>
+        <v>8753.790000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>295503</v>
+        <v>284418</v>
       </c>
       <c r="G140" t="n">
-        <v>5287</v>
+        <v>5089</v>
       </c>
       <c r="H140" t="n">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="I140" t="n">
         <v>23</v>
       </c>
       <c r="J140" t="n">
-        <v>15822.8</v>
+        <v>15355.53</v>
       </c>
       <c r="K140" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="141">
@@ -8619,25 +8619,25 @@
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>12003.76</v>
+        <v>11553.47</v>
       </c>
       <c r="F141" t="n">
-        <v>397525</v>
+        <v>382613</v>
       </c>
       <c r="G141" t="n">
-        <v>12162</v>
+        <v>11706</v>
       </c>
       <c r="H141" t="n">
-        <v>2140</v>
+        <v>2059</v>
       </c>
       <c r="I141" t="n">
         <v>23</v>
       </c>
       <c r="J141" t="n">
-        <v>15532.49</v>
+        <v>15073.79</v>
       </c>
       <c r="K141" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="142">
@@ -8656,25 +8656,25 @@
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>12012.36</v>
+        <v>11829.02</v>
       </c>
       <c r="F142" t="n">
-        <v>368362</v>
+        <v>362740</v>
       </c>
       <c r="G142" t="n">
-        <v>4465</v>
+        <v>4396</v>
       </c>
       <c r="H142" t="n">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="I142" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J142" t="n">
-        <v>13990.61</v>
+        <v>14218.12</v>
       </c>
       <c r="K142" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="143">
@@ -8693,25 +8693,25 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>15619.25</v>
+        <v>15380.84</v>
       </c>
       <c r="F143" t="n">
-        <v>417753</v>
+        <v>411376</v>
       </c>
       <c r="G143" t="n">
-        <v>5081</v>
+        <v>5003</v>
       </c>
       <c r="H143" t="n">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="I143" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J143" t="n">
-        <v>13719.61</v>
+        <v>13942.71</v>
       </c>
       <c r="K143" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="144">
@@ -8734,25 +8734,25 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11268.18</v>
+        <v>11096.19</v>
       </c>
       <c r="F144" t="n">
-        <v>421546</v>
+        <v>415111</v>
       </c>
       <c r="G144" t="n">
-        <v>7386</v>
+        <v>7273</v>
       </c>
       <c r="H144" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="I144" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J144" t="n">
-        <v>13369.09</v>
+        <v>13586.49</v>
       </c>
       <c r="K144" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="145">
@@ -8771,25 +8771,25 @@
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>14151.55</v>
+        <v>13935.55</v>
       </c>
       <c r="F145" t="n">
-        <v>494205</v>
+        <v>486662</v>
       </c>
       <c r="G145" t="n">
-        <v>14850</v>
+        <v>14624</v>
       </c>
       <c r="H145" t="n">
-        <v>2146</v>
+        <v>2113</v>
       </c>
       <c r="I145" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J145" t="n">
-        <v>13904.93</v>
+        <v>14131.05</v>
       </c>
       <c r="K145" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="146">
@@ -8812,25 +8812,25 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>9293.549999999999</v>
+        <v>9151.700000000001</v>
       </c>
       <c r="F146" t="n">
-        <v>246713</v>
+        <v>242948</v>
       </c>
       <c r="G146" t="n">
-        <v>2449</v>
+        <v>2412</v>
       </c>
       <c r="H146" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I146" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J146" t="n">
-        <v>13946.57</v>
+        <v>14173.37</v>
       </c>
       <c r="K146" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="147">
@@ -8853,25 +8853,25 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>13230.83</v>
+        <v>11191.26</v>
       </c>
       <c r="F147" t="n">
-        <v>482186</v>
+        <v>407855</v>
       </c>
       <c r="G147" t="n">
-        <v>12269</v>
+        <v>10378</v>
       </c>
       <c r="H147" t="n">
-        <v>1968</v>
+        <v>1664</v>
       </c>
       <c r="I147" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J147" t="n">
-        <v>24139.94</v>
+        <v>19978.49</v>
       </c>
       <c r="K147" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="148">
@@ -8890,25 +8890,25 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>9486.379999999999</v>
+        <v>8024.03</v>
       </c>
       <c r="F148" t="n">
-        <v>305089</v>
+        <v>258059</v>
       </c>
       <c r="G148" t="n">
-        <v>8812</v>
+        <v>7453</v>
       </c>
       <c r="H148" t="n">
-        <v>567</v>
+        <v>479</v>
       </c>
       <c r="I148" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J148" t="n">
-        <v>24193.14</v>
+        <v>20022.52</v>
       </c>
       <c r="K148" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="149">
@@ -8931,25 +8931,25 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>13350.89</v>
+        <v>11292.82</v>
       </c>
       <c r="F149" t="n">
-        <v>632111</v>
+        <v>534669</v>
       </c>
       <c r="G149" t="n">
-        <v>15239</v>
+        <v>12890</v>
       </c>
       <c r="H149" t="n">
-        <v>1109</v>
+        <v>938</v>
       </c>
       <c r="I149" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J149" t="n">
-        <v>23855.53</v>
+        <v>19743.11</v>
       </c>
       <c r="K149" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="150">
@@ -8972,25 +8972,25 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>13150.07</v>
+        <v>11122.95</v>
       </c>
       <c r="F150" t="n">
-        <v>623214</v>
+        <v>527144</v>
       </c>
       <c r="G150" t="n">
-        <v>21578</v>
+        <v>18252</v>
       </c>
       <c r="H150" t="n">
-        <v>2530</v>
+        <v>2140</v>
       </c>
       <c r="I150" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J150" t="n">
-        <v>25676.32</v>
+        <v>21250.02</v>
       </c>
       <c r="K150" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="151">
@@ -9009,25 +9009,25 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>7607.48</v>
+        <v>6434.78</v>
       </c>
       <c r="F151" t="n">
-        <v>202240</v>
+        <v>171064</v>
       </c>
       <c r="G151" t="n">
-        <v>6120</v>
+        <v>5176</v>
       </c>
       <c r="H151" t="n">
-        <v>607</v>
+        <v>513</v>
       </c>
       <c r="I151" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J151" t="n">
-        <v>23524.46</v>
+        <v>19469.12</v>
       </c>
       <c r="K151" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="152">
@@ -9050,25 +9050,25 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>700.91</v>
+        <v>1041.93</v>
       </c>
       <c r="F152" t="n">
-        <v>42795</v>
+        <v>63617</v>
       </c>
       <c r="G152" t="n">
-        <v>1048</v>
+        <v>1559</v>
       </c>
       <c r="H152" t="n">
-        <v>177</v>
+        <v>263</v>
       </c>
       <c r="I152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
-        <v>1001.68</v>
+        <v>1626.93</v>
       </c>
       <c r="K152" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="153">
@@ -9091,25 +9091,25 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>407.9</v>
+        <v>606.35</v>
       </c>
       <c r="F153" t="n">
-        <v>12026</v>
+        <v>17877</v>
       </c>
       <c r="G153" t="n">
-        <v>414</v>
+        <v>616</v>
       </c>
       <c r="H153" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="I153" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J153" t="n">
-        <v>1017.92</v>
+        <v>1653.31</v>
       </c>
       <c r="K153" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="154">
@@ -9128,25 +9128,25 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>409.77</v>
+        <v>609.14</v>
       </c>
       <c r="F154" t="n">
-        <v>11084</v>
+        <v>16477</v>
       </c>
       <c r="G154" t="n">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="H154" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
-        <v>481.7</v>
+        <v>1043.18</v>
       </c>
       <c r="K154" t="n">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="155">
@@ -9165,25 +9165,25 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>719.71</v>
+        <v>1069.87</v>
       </c>
       <c r="F155" t="n">
-        <v>18696</v>
+        <v>27793</v>
       </c>
       <c r="G155" t="n">
-        <v>596</v>
+        <v>886</v>
       </c>
       <c r="H155" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J155" t="n">
-        <v>1024.93</v>
+        <v>1664.7</v>
       </c>
       <c r="K155" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="156">
@@ -9206,25 +9206,25 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>593.8</v>
+        <v>882.71</v>
       </c>
       <c r="F156" t="n">
-        <v>17223</v>
+        <v>25602</v>
       </c>
       <c r="G156" t="n">
-        <v>263</v>
+        <v>391</v>
       </c>
       <c r="H156" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
-        <v>252.25</v>
+        <v>546.26</v>
       </c>
       <c r="K156" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="157">
@@ -9247,25 +9247,25 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>485.92</v>
+        <v>690.97</v>
       </c>
       <c r="F157" t="n">
-        <v>19556</v>
+        <v>27809</v>
       </c>
       <c r="G157" t="n">
-        <v>579</v>
+        <v>824</v>
       </c>
       <c r="H157" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="I157" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J157" t="n">
-        <v>1855.83</v>
+        <v>2229.74</v>
       </c>
       <c r="K157" t="n">
-        <v>3.82</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="158">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>项目7</t>
+          <t>项目8</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9288,25 +9288,25 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>449.62</v>
+        <v>639.35</v>
       </c>
       <c r="F158" t="n">
-        <v>28775</v>
+        <v>40918</v>
       </c>
       <c r="G158" t="n">
-        <v>863</v>
+        <v>1228</v>
       </c>
       <c r="H158" t="n">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="I158" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J158" t="n">
-        <v>1766.77</v>
+        <v>2358.6</v>
       </c>
       <c r="K158" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="159">
@@ -9329,25 +9329,25 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>482.14</v>
+        <v>685.6</v>
       </c>
       <c r="F159" t="n">
-        <v>13033</v>
+        <v>18533</v>
       </c>
       <c r="G159" t="n">
-        <v>269</v>
+        <v>383</v>
       </c>
       <c r="H159" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J159" t="n">
-        <v>762.02</v>
+        <v>1186.83</v>
       </c>
       <c r="K159" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="160">
@@ -9370,25 +9370,25 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>542.42</v>
+        <v>771.33</v>
       </c>
       <c r="F160" t="n">
-        <v>35724</v>
+        <v>50800</v>
       </c>
       <c r="G160" t="n">
-        <v>887</v>
+        <v>1261</v>
       </c>
       <c r="H160" t="n">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="I160" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J160" t="n">
-        <v>1772.49</v>
+        <v>2366.23</v>
       </c>
       <c r="K160" t="n">
-        <v>3.27</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="161">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>项目15</t>
+          <t>项目16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9411,25 +9411,25 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>547.63</v>
+        <v>778.73</v>
       </c>
       <c r="F161" t="n">
-        <v>14628</v>
+        <v>20801</v>
       </c>
       <c r="G161" t="n">
-        <v>495</v>
+        <v>704</v>
       </c>
       <c r="H161" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J161" t="n">
-        <v>994.05</v>
+        <v>1393.39</v>
       </c>
       <c r="K161" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="162">
@@ -9448,25 +9448,25 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>566.37</v>
+        <v>514.08</v>
       </c>
       <c r="F162" t="n">
-        <v>29931</v>
+        <v>27168</v>
       </c>
       <c r="G162" t="n">
-        <v>832</v>
+        <v>755</v>
       </c>
       <c r="H162" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
-        <v>1666.03</v>
+        <v>1429.75</v>
       </c>
       <c r="K162" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="163">
@@ -9485,25 +9485,25 @@
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>460.06</v>
+        <v>417.59</v>
       </c>
       <c r="F163" t="n">
-        <v>22472</v>
+        <v>20398</v>
       </c>
       <c r="G163" t="n">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="H163" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J163" t="n">
-        <v>1759.95</v>
+        <v>1510.35</v>
       </c>
       <c r="K163" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="164">
@@ -9522,25 +9522,25 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>518.23</v>
+        <v>470.39</v>
       </c>
       <c r="F164" t="n">
-        <v>19759</v>
+        <v>17935</v>
       </c>
       <c r="G164" t="n">
-        <v>570</v>
+        <v>517</v>
       </c>
       <c r="H164" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J164" t="n">
-        <v>1601.8</v>
+        <v>1374.63</v>
       </c>
       <c r="K164" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="165">
@@ -9559,25 +9559,25 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>434.68</v>
+        <v>394.55</v>
       </c>
       <c r="F165" t="n">
-        <v>13143</v>
+        <v>11930</v>
       </c>
       <c r="G165" t="n">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="H165" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J165" t="n">
-        <v>1665.35</v>
+        <v>1429.16</v>
       </c>
       <c r="K165" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="166">
@@ -9596,25 +9596,25 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>509.01</v>
+        <v>462.04</v>
       </c>
       <c r="F166" t="n">
-        <v>14761</v>
+        <v>13399</v>
       </c>
       <c r="G166" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="H166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
       </c>
       <c r="J166" t="n">
-        <v>321.65</v>
+        <v>345.04</v>
       </c>
       <c r="K166" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="167">
@@ -9633,25 +9633,25 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
-        <v>631.52</v>
+        <v>530.66</v>
       </c>
       <c r="F167" t="n">
-        <v>22270</v>
+        <v>18713</v>
       </c>
       <c r="G167" t="n">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="H167" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J167" t="n">
-        <v>1783.28</v>
+        <v>1587.37</v>
       </c>
       <c r="K167" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="168">
@@ -9670,25 +9670,25 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>707.1</v>
+        <v>594.17</v>
       </c>
       <c r="F168" t="n">
-        <v>29112</v>
+        <v>24463</v>
       </c>
       <c r="G168" t="n">
-        <v>828</v>
+        <v>695</v>
       </c>
       <c r="H168" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="I168" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J168" t="n">
-        <v>2138.79</v>
+        <v>1943.48</v>
       </c>
       <c r="K168" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="169">
@@ -9707,25 +9707,25 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>754.49</v>
+        <v>633.99</v>
       </c>
       <c r="F169" t="n">
-        <v>30794</v>
+        <v>25876</v>
       </c>
       <c r="G169" t="n">
-        <v>835</v>
+        <v>701</v>
       </c>
       <c r="H169" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J169" t="n">
-        <v>2041.22</v>
+        <v>1854.82</v>
       </c>
       <c r="K169" t="n">
-        <v>2.71</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="170">
@@ -9739,30 +9739,30 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>项目8</t>
+          <t>项目9</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>1009.52</v>
+        <v>848.29</v>
       </c>
       <c r="F170" t="n">
-        <v>49523</v>
+        <v>41614</v>
       </c>
       <c r="G170" t="n">
-        <v>971</v>
+        <v>816</v>
       </c>
       <c r="H170" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="I170" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J170" t="n">
-        <v>2158.95</v>
+        <v>1961.8</v>
       </c>
       <c r="K170" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="171">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>651.79</v>
+        <v>547.71</v>
       </c>
       <c r="F171" t="n">
-        <v>23766</v>
+        <v>19971</v>
       </c>
       <c r="G171" t="n">
-        <v>766</v>
+        <v>644</v>
       </c>
       <c r="H171" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="I171" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J171" t="n">
-        <v>2067.54</v>
+        <v>1878.74</v>
       </c>
       <c r="K171" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="172">
@@ -9818,25 +9818,25 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>873.3200000000001</v>
+        <v>730.67</v>
       </c>
       <c r="F172" t="n">
-        <v>36012</v>
+        <v>30129</v>
       </c>
       <c r="G172" t="n">
-        <v>473</v>
+        <v>395</v>
       </c>
       <c r="H172" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I172" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J172" t="n">
-        <v>5301.3</v>
+        <v>4595.82</v>
       </c>
       <c r="K172" t="n">
-        <v>6.07</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="173">
@@ -9855,25 +9855,25 @@
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>1275.61</v>
+        <v>1067.25</v>
       </c>
       <c r="F173" t="n">
-        <v>62133</v>
+        <v>51984</v>
       </c>
       <c r="G173" t="n">
-        <v>2051</v>
+        <v>1716</v>
       </c>
       <c r="H173" t="n">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="I173" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J173" t="n">
-        <v>4890.15</v>
+        <v>4239.38</v>
       </c>
       <c r="K173" t="n">
-        <v>3.83</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="174">
@@ -9887,30 +9887,30 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>项目9</t>
+          <t>项目10</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>1468.3</v>
+        <v>1228.46</v>
       </c>
       <c r="F174" t="n">
-        <v>61189</v>
+        <v>51194</v>
       </c>
       <c r="G174" t="n">
-        <v>1330</v>
+        <v>1113</v>
       </c>
       <c r="H174" t="n">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I174" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J174" t="n">
-        <v>5130.41</v>
+        <v>4447.68</v>
       </c>
       <c r="K174" t="n">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="175">
@@ -9929,25 +9929,25 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>1157.7</v>
+        <v>968.6</v>
       </c>
       <c r="F175" t="n">
-        <v>42354</v>
+        <v>35436</v>
       </c>
       <c r="G175" t="n">
-        <v>871</v>
+        <v>729</v>
       </c>
       <c r="H175" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="I175" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
-        <v>4936.96</v>
+        <v>4279.97</v>
       </c>
       <c r="K175" t="n">
-        <v>4.26</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="176">
@@ -9961,30 +9961,30 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>项目20</t>
+          <t>项目1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>856.28</v>
+        <v>716.4</v>
       </c>
       <c r="F176" t="n">
-        <v>24017</v>
+        <v>20094</v>
       </c>
       <c r="G176" t="n">
-        <v>625</v>
+        <v>523</v>
       </c>
       <c r="H176" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="I176" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J176" t="n">
-        <v>5238.41</v>
+        <v>4541.3</v>
       </c>
       <c r="K176" t="n">
-        <v>6.12</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="177">
@@ -10003,25 +10003,25 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>871.45</v>
+        <v>761.04</v>
       </c>
       <c r="F177" t="n">
-        <v>30542</v>
+        <v>26672</v>
       </c>
       <c r="G177" t="n">
-        <v>1009</v>
+        <v>881</v>
       </c>
       <c r="H177" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="I177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
-        <v>1821.59</v>
+        <v>1614.18</v>
       </c>
       <c r="K177" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="178">
@@ -10040,25 +10040,25 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>517.5700000000001</v>
+        <v>451.99</v>
       </c>
       <c r="F178" t="n">
-        <v>29525</v>
+        <v>25784</v>
       </c>
       <c r="G178" t="n">
-        <v>585</v>
+        <v>510</v>
       </c>
       <c r="H178" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
-        <v>1376.11</v>
+        <v>1083.93</v>
       </c>
       <c r="K178" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="179">
@@ -10077,25 +10077,25 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="n">
-        <v>516.08</v>
+        <v>450.69</v>
       </c>
       <c r="F179" t="n">
-        <v>14397</v>
+        <v>12573</v>
       </c>
       <c r="G179" t="n">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="H179" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J179" t="n">
-        <v>1731.07</v>
+        <v>1533.97</v>
       </c>
       <c r="K179" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="180">
@@ -10109,30 +10109,30 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>项目8</t>
+          <t>项目9</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>528.21</v>
+        <v>461.29</v>
       </c>
       <c r="F180" t="n">
-        <v>19766</v>
+        <v>17261</v>
       </c>
       <c r="G180" t="n">
-        <v>498</v>
+        <v>435</v>
       </c>
       <c r="H180" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J180" t="n">
-        <v>1841.48</v>
+        <v>1631.81</v>
       </c>
       <c r="K180" t="n">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="181">
@@ -10151,25 +10151,25 @@
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>624.8</v>
+        <v>545.64</v>
       </c>
       <c r="F181" t="n">
-        <v>39252</v>
+        <v>34279</v>
       </c>
       <c r="G181" t="n">
-        <v>536</v>
+        <v>468</v>
       </c>
       <c r="H181" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I181" t="n">
         <v>3</v>
       </c>
       <c r="J181" t="n">
-        <v>1327.51</v>
+        <v>1568.48</v>
       </c>
       <c r="K181" t="n">
-        <v>2.12</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
